--- a/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17bc974f5891b333/Documents/ProPASS/Harmo/NHATS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="8_{5005C4B8-8269-4712-9267-05709C8265AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4A0AD7B-14FE-4760-88D4-9B140D6AB843}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="8_{5005C4B8-8269-4712-9267-05709C8265AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{339FDDB2-46A3-461B-A141-A096D22A068A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F744FAC3-0BAB-4C7A-92B3-0824573F48DB}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="405">
   <si>
     <t>index</t>
   </si>
@@ -975,12 +975,6 @@
     <t>NHATS SAMPLED PERSON ID</t>
   </si>
   <si>
-    <t>r5dgender</t>
-  </si>
-  <si>
-    <t>R5 D GENDER OF SP</t>
-  </si>
-  <si>
     <t>-7= RF;
 -8= DK;
 -1= Inapplicable;
@@ -1071,9 +1065,6 @@
 3 = Good;
 4 = Fair;
 5 = Poor</t>
-  </si>
-  <si>
-    <t>recode (5 = 1; 4 = 2; 3 = 3; c(1,2) = 4; ELSE = NA)</t>
   </si>
   <si>
     <t xml:space="preserve">-7 = DF;
@@ -1099,9 +1090,6 @@
 1 = YES;
 2 = NO
 7 = PREVIOUSLY REPORTED</t>
-  </si>
-  <si>
-    <t>recode (c(1,7) = 1; 2 = 0; c(-9,-8,-7) = NA; -1 = NA; ELSE = NA)</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1484,13 +1472,6 @@
   </si>
   <si>
     <t>case_when(
-dt11getoplcs1 == 1 | ha11howgtstr7 == 1 ~ 1;
-dt11getoplcs1 == 2 &amp; ha11howgtstr7 == 2 ~ 0;
-TRUE ~ NA_integer_
-)</t>
-  </si>
-  <si>
-    <t>case_when(
   hw12howtallft %in% c(-7, -8, -9, -1) |
     hw12howtallin %in% c(-7, -8, -9, -1) |
     hw12currweigh %in% c(-7, -8, -9, -1) ~ NA_real_,
@@ -1624,6 +1605,37 @@
 715 = Exercise (gym, yoga, swimming, dancing, etc.)
 737 = Leisure travel
 799 = Other active leisure</t>
+  </si>
+  <si>
+    <t>recode(c(1,7) = 1; 2 = 0; c(-9,-8,-7) = NA; -1 = NA; ELSE = NA)</t>
+  </si>
+  <si>
+    <t>recode(5 = 1; 4 = 2; 3 = 3; c(1,2) = 4; ELSE = NA)</t>
+  </si>
+  <si>
+    <t>r12dgender</t>
+  </si>
+  <si>
+    <t>R12 D GENDER OF SP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recode(5=1; 4 = 2; 3= 3; 1:2=4; ELSE=NA) </t>
+  </si>
+  <si>
+    <t>-9 = Missing; 
+-7 = RF;
+-8 = DK;
+-1 = Inapplicable;
+1 = YES;
+2 = NO
+7 = PREVIOUSLY REPORTED</t>
+  </si>
+  <si>
+    <t>case_when(
+dt12getoplcs1 == 1 | ha12howgtstr7 == 1 ~ 1;
+dt12getoplcs1 == 2 &amp; ha12howgtstr7 == 2 ~ 0;
+TRUE ~ NA_integer_
+)</t>
   </si>
 </sst>
 </file>
@@ -1746,7 +1758,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1785,13 +1797,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2168,7 +2173,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>3</v>
@@ -2177,10 +2182,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>1</v>
@@ -2192,10 +2197,10 @@
         <v>275</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>277</v>
@@ -2210,7 +2215,7 @@
         <v>280</v>
       </c>
       <c r="R1" s="10" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="S1" s="14" t="s">
         <v>9</v>
@@ -2231,7 +2236,7 @@
         <v>8</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
@@ -2254,7 +2259,7 @@
         <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J2" t="s">
         <v>284</v>
@@ -2267,14 +2272,14 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O2" s="16"/>
       <c r="P2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="R2" s="16"/>
       <c r="S2" s="4"/>
@@ -2285,7 +2290,7 @@
         <v>27</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="X2" s="4" t="s">
         <v>284</v>
@@ -2300,30 +2305,30 @@
         <v>283</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K3"/>
       <c r="N3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O3" s="16"/>
       <c r="Q3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
@@ -2334,14 +2339,14 @@
         <v>27</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="X3" s="4">
         <v>1</v>
       </c>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" ht="114" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2365,18 +2370,18 @@
       </c>
       <c r="H4" s="2"/>
       <c r="I4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O4" s="16"/>
       <c r="R4" s="4"/>
@@ -2385,7 +2390,7 @@
         <v>14</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>14</v>
@@ -2394,7 +2399,7 @@
         <v>14</v>
       </c>
       <c r="Y4" s="11" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
@@ -2420,27 +2425,27 @@
         <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>382</v>
-      </c>
-      <c r="J5" t="s">
+        <v>378</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="K5" t="s">
+        <v>401</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="K5" t="s">
-        <v>287</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>288</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q5" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U5" t="s">
         <v>26</v>
@@ -2452,7 +2457,7 @@
         <v>38</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
@@ -2479,25 +2484,27 @@
       </c>
       <c r="H6" s="2"/>
       <c r="I6" t="s">
-        <v>382</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>340</v>
+        <v>378</v>
+      </c>
+      <c r="J6" t="s">
+        <v>336</v>
       </c>
       <c r="K6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="N6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O6" s="16"/>
       <c r="P6" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q6" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="R6" t="s">
         <v>32</v>
@@ -2538,15 +2545,15 @@
         <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O7" s="16"/>
       <c r="S7" s="2"/>
@@ -2563,7 +2570,7 @@
         <v>14</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -2589,27 +2596,27 @@
         <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="K8" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O8" s="16"/>
       <c r="P8" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q8" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U8" t="s">
         <v>26</v>
@@ -2621,7 +2628,7 @@
         <v>38</v>
       </c>
       <c r="X8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
@@ -2647,27 +2654,27 @@
         <v>46</v>
       </c>
       <c r="I9" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J9" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="K9" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O9" s="16"/>
       <c r="P9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q9" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U9" s="4" t="s">
         <v>26</v>
@@ -2679,7 +2686,7 @@
         <v>51</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -2702,26 +2709,26 @@
         <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J10" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="K10" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="N10" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O10" s="16"/>
       <c r="P10" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q10" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="R10" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="U10" t="s">
         <v>26</v>
@@ -2756,26 +2763,26 @@
         <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J11" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="K11" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="N11" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O11" s="16"/>
       <c r="P11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q11" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U11" t="s">
         <v>26</v>
@@ -2813,27 +2820,27 @@
         <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J12" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="K12" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="L12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M12"/>
       <c r="N12" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O12" s="16"/>
       <c r="P12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q12" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U12" t="s">
         <v>26</v>
@@ -2845,7 +2852,7 @@
         <v>38</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="171" x14ac:dyDescent="0.45">
@@ -2871,27 +2878,27 @@
         <v>62</v>
       </c>
       <c r="I13" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J13" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="K13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O13" s="16"/>
       <c r="U13" t="s">
         <v>14</v>
       </c>
       <c r="V13" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="W13" t="s">
         <v>14</v>
@@ -2900,7 +2907,7 @@
         <v>14</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="171" x14ac:dyDescent="0.45">
@@ -2926,27 +2933,27 @@
         <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J14" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="K14" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O14" s="16"/>
       <c r="P14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q14" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U14" t="s">
         <v>26</v>
@@ -2958,10 +2965,10 @@
         <v>38</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>15</v>
       </c>
@@ -2984,32 +2991,32 @@
         <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>382</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>391</v>
+        <v>378</v>
+      </c>
+      <c r="J15" t="s">
+        <v>386</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="L15" s="17" t="s">
-        <v>392</v>
+        <v>373</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>387</v>
       </c>
       <c r="N15" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O15" s="16"/>
       <c r="P15" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q15" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U15" s="4" t="s">
         <v>14</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="W15" s="4" t="s">
         <v>14</v>
@@ -3017,8 +3024,8 @@
       <c r="X15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Y15" s="19" t="s">
-        <v>393</v>
+      <c r="Y15" s="11" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
@@ -3045,29 +3052,29 @@
       </c>
       <c r="H16" s="2"/>
       <c r="I16" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N16" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O16" s="16"/>
       <c r="P16" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q16" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="R16" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="U16" t="s">
         <v>26</v>
@@ -3079,7 +3086,7 @@
         <v>75</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
@@ -3105,20 +3112,20 @@
         <v>78</v>
       </c>
       <c r="I17" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J17" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N17" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O17" s="16"/>
       <c r="P17" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U17" s="4" t="s">
         <v>26</v>
@@ -3127,7 +3134,7 @@
         <v>27</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="X17" s="4">
         <v>1</v>
@@ -3157,23 +3164,23 @@
       </c>
       <c r="H18" s="2"/>
       <c r="I18" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J18" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="K18" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N18" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O18" s="16"/>
       <c r="P18" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q18" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="R18" t="s">
         <v>82</v>
@@ -3188,7 +3195,7 @@
         <v>75</v>
       </c>
       <c r="X18" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
@@ -3214,20 +3221,20 @@
         <v>78</v>
       </c>
       <c r="I19" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J19" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N19" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O19" s="16"/>
       <c r="P19" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q19" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U19" s="4" t="s">
         <v>26</v>
@@ -3236,7 +3243,7 @@
         <v>27</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="X19" s="4">
         <v>1</v>
@@ -3265,26 +3272,26 @@
         <v>87</v>
       </c>
       <c r="I20" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="N20" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O20" s="16"/>
       <c r="P20" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q20" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="R20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U20" t="s">
         <v>26</v>
@@ -3296,7 +3303,7 @@
         <v>51</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
@@ -3323,23 +3330,23 @@
       </c>
       <c r="H21" s="2"/>
       <c r="I21" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J21" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="K21" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="N21" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O21" s="16"/>
       <c r="P21" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q21" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="R21" t="s">
         <v>74</v>
@@ -3354,7 +3361,7 @@
         <v>75</v>
       </c>
       <c r="X21" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="57" x14ac:dyDescent="0.45">
@@ -3380,27 +3387,27 @@
         <v>78</v>
       </c>
       <c r="I22" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J22" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="K22" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O22" s="16"/>
       <c r="P22" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q22" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U22" t="s">
         <v>26</v>
@@ -3412,7 +3419,7 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
@@ -3438,17 +3445,17 @@
         <v>94</v>
       </c>
       <c r="I23" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J23" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N23" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O23" s="16"/>
       <c r="P23" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
@@ -3471,13 +3478,13 @@
         <v>13</v>
       </c>
       <c r="I24" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J24" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N24" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O24" s="16"/>
       <c r="U24" s="4" t="s">
@@ -3516,13 +3523,13 @@
         <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J25" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N25" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O25" s="16"/>
       <c r="U25" s="4" t="s">
@@ -3561,13 +3568,13 @@
         <v>100</v>
       </c>
       <c r="I26" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J26" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N26" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O26" s="16"/>
       <c r="U26" s="4" t="s">
@@ -3606,13 +3613,13 @@
         <v>106</v>
       </c>
       <c r="I27" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J27" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N27" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O27" s="16"/>
       <c r="U27" s="4" t="s">
@@ -3652,13 +3659,13 @@
       </c>
       <c r="H28" s="2"/>
       <c r="I28" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N28" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O28" s="16"/>
       <c r="U28" s="4" t="s">
@@ -3697,13 +3704,13 @@
         <v>112</v>
       </c>
       <c r="I29" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J29" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N29" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O29" s="16"/>
       <c r="U29" s="4" t="s">
@@ -3742,13 +3749,13 @@
         <v>115</v>
       </c>
       <c r="I30" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J30" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N30" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O30" s="16"/>
       <c r="U30" s="4" t="s">
@@ -3787,13 +3794,13 @@
         <v>118</v>
       </c>
       <c r="I31" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J31" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N31" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O31" s="16"/>
       <c r="U31" s="4" t="s">
@@ -3832,13 +3839,13 @@
         <v>121</v>
       </c>
       <c r="I32" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J32" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N32" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O32" s="16"/>
       <c r="U32" s="4" t="s">
@@ -3877,13 +3884,13 @@
         <v>121</v>
       </c>
       <c r="I33" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J33" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N33" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O33" s="16"/>
       <c r="U33" s="4" t="s">
@@ -3922,13 +3929,13 @@
         <v>121</v>
       </c>
       <c r="I34" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J34" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N34" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O34" s="16"/>
       <c r="U34" s="4" t="s">
@@ -3967,13 +3974,13 @@
         <v>121</v>
       </c>
       <c r="I35" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J35" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N35" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O35" s="16"/>
       <c r="U35" s="4" t="s">
@@ -4012,13 +4019,13 @@
         <v>121</v>
       </c>
       <c r="I36" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J36" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N36" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O36" s="16"/>
       <c r="U36" s="4" t="s">
@@ -4057,13 +4064,13 @@
         <v>132</v>
       </c>
       <c r="I37" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J37" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N37" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O37" s="16"/>
       <c r="U37" s="4" t="s">
@@ -4103,13 +4110,13 @@
       </c>
       <c r="H38" s="2"/>
       <c r="I38" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J38" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N38" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O38" s="16"/>
       <c r="U38" s="4" t="s">
@@ -4148,15 +4155,15 @@
         <v>140</v>
       </c>
       <c r="I39" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J39" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O39" s="16"/>
       <c r="P39"/>
@@ -4200,13 +4207,13 @@
       </c>
       <c r="H40" s="2"/>
       <c r="I40" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J40" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N40" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O40" s="16"/>
       <c r="U40" s="4" t="s">
@@ -4245,13 +4252,13 @@
         <v>140</v>
       </c>
       <c r="I41" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N41" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O41" s="16"/>
       <c r="U41" s="4" t="s">
@@ -4290,13 +4297,13 @@
         <v>149</v>
       </c>
       <c r="I42" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N42" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O42" s="16"/>
       <c r="U42" s="4" t="s">
@@ -4336,13 +4343,13 @@
       </c>
       <c r="H43" s="2"/>
       <c r="I43" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J43" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N43" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O43" s="16"/>
       <c r="U43" s="4" t="s">
@@ -4381,13 +4388,13 @@
         <v>156</v>
       </c>
       <c r="I44" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J44" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N44" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O44" s="16"/>
       <c r="U44" s="4" t="s">
@@ -4426,20 +4433,20 @@
         <v>160</v>
       </c>
       <c r="I45" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J45" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="K45" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M45" s="5"/>
       <c r="N45" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O45" s="16"/>
       <c r="S45" s="2"/>
@@ -4447,7 +4454,7 @@
         <v>14</v>
       </c>
       <c r="V45" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="W45" s="4" t="s">
         <v>14</v>
@@ -4456,7 +4463,7 @@
         <v>14</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
@@ -4482,10 +4489,10 @@
         <v>163</v>
       </c>
       <c r="I46" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J46" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>164</v>
@@ -4495,14 +4502,14 @@
       </c>
       <c r="M46" s="5"/>
       <c r="N46" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O46" s="16"/>
       <c r="U46" t="s">
         <v>14</v>
       </c>
       <c r="V46" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>14</v>
@@ -4535,27 +4542,27 @@
       </c>
       <c r="H47" s="2"/>
       <c r="I47" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J47" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="K47" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>165</v>
       </c>
       <c r="M47" s="5"/>
       <c r="N47" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O47" s="16"/>
       <c r="P47" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q47" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U47" t="s">
         <v>26</v>
@@ -4567,7 +4574,7 @@
         <v>51</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
@@ -4593,27 +4600,27 @@
         <v>171</v>
       </c>
       <c r="I48" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J48" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K48" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M48" s="5"/>
       <c r="N48" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O48" s="16"/>
       <c r="P48" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q48" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U48" t="s">
         <v>26</v>
@@ -4625,7 +4632,10 @@
         <v>38</v>
       </c>
       <c r="X48" t="s">
-        <v>308</v>
+        <v>399</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="49" spans="1:25" ht="213.75" x14ac:dyDescent="0.45">
@@ -4651,27 +4661,27 @@
         <v>175</v>
       </c>
       <c r="I49" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J49" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="M49" s="5"/>
       <c r="N49" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O49" s="16"/>
       <c r="P49" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q49" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="S49" s="2"/>
       <c r="U49" t="s">
@@ -4684,10 +4694,10 @@
         <v>51</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="50" spans="1:25" ht="213.75" x14ac:dyDescent="0.45">
@@ -4713,27 +4723,27 @@
         <v>175</v>
       </c>
       <c r="I50" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J50" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="M50" s="5"/>
       <c r="N50" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O50" s="16"/>
       <c r="P50" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q50" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="S50" s="2"/>
       <c r="U50" t="s">
@@ -4746,10 +4756,10 @@
         <v>51</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
@@ -4775,27 +4785,27 @@
         <v>175</v>
       </c>
       <c r="I51" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J51" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="K51" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>182</v>
       </c>
       <c r="M51" s="5"/>
       <c r="N51" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O51" s="16"/>
       <c r="P51" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q51" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U51" t="s">
         <v>26</v>
@@ -4807,7 +4817,7 @@
         <v>51</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
@@ -4833,15 +4843,15 @@
         <v>186</v>
       </c>
       <c r="I52" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J52" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O52" s="16"/>
       <c r="U52" s="4" t="s">
@@ -4880,27 +4890,27 @@
         <v>175</v>
       </c>
       <c r="I53" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="L53" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M53" s="5"/>
       <c r="N53" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O53" s="16"/>
       <c r="P53" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q53" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U53" t="s">
         <v>26</v>
@@ -4912,7 +4922,7 @@
         <v>51</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -4938,13 +4948,13 @@
         <v>175</v>
       </c>
       <c r="I54" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J54" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N54" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O54" s="16"/>
       <c r="U54" s="4" t="s">
@@ -4983,15 +4993,15 @@
         <v>175</v>
       </c>
       <c r="I55" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J55" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O55" s="16"/>
       <c r="U55" s="4" t="s">
@@ -5030,15 +5040,15 @@
         <v>175</v>
       </c>
       <c r="I56" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J56" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O56" s="16"/>
       <c r="U56" s="4" t="s">
@@ -5077,13 +5087,13 @@
         <v>175</v>
       </c>
       <c r="I57" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J57" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N57" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O57" s="16"/>
       <c r="U57" s="4" t="s">
@@ -5122,13 +5132,13 @@
         <v>175</v>
       </c>
       <c r="I58" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J58" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N58" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O58" s="16"/>
       <c r="U58" s="4" t="s">
@@ -5164,13 +5174,13 @@
         <v>16</v>
       </c>
       <c r="I59" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J59" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N59" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O59" s="16"/>
       <c r="U59" s="4" t="s">
@@ -5206,13 +5216,13 @@
         <v>16</v>
       </c>
       <c r="I60" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J60" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N60" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O60" s="16"/>
       <c r="U60" s="4" t="s">
@@ -5248,13 +5258,13 @@
         <v>16</v>
       </c>
       <c r="I61" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J61" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N61" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O61" s="16"/>
       <c r="U61" s="4" t="s">
@@ -5290,13 +5300,13 @@
         <v>16</v>
       </c>
       <c r="I62" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J62" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N62" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O62" s="16"/>
       <c r="U62" s="4" t="s">
@@ -5332,13 +5342,13 @@
         <v>16</v>
       </c>
       <c r="I63" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J63" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N63" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O63" s="16"/>
       <c r="S63" s="2"/>
@@ -5376,13 +5386,13 @@
         <v>16</v>
       </c>
       <c r="I64" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J64" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N64" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O64" s="16"/>
       <c r="U64" s="4" t="s">
@@ -5419,13 +5429,13 @@
       </c>
       <c r="H65" s="2"/>
       <c r="I65" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J65" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N65" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O65" s="16"/>
       <c r="U65" s="4" t="s">
@@ -5464,27 +5474,27 @@
         <v>216</v>
       </c>
       <c r="I66" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J66" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K66" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>310</v>
+        <v>403</v>
       </c>
       <c r="M66" s="5"/>
       <c r="N66" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O66" s="16"/>
       <c r="P66" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q66" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="S66" s="2"/>
       <c r="U66" t="s">
@@ -5497,7 +5507,7 @@
         <v>38</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>311</v>
+        <v>398</v>
       </c>
       <c r="Y66" s="2"/>
     </row>
@@ -5525,13 +5535,13 @@
       </c>
       <c r="H67" s="2"/>
       <c r="I67" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J67" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N67" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O67" s="16"/>
       <c r="U67" s="4" t="s">
@@ -5570,13 +5580,13 @@
         <v>222</v>
       </c>
       <c r="I68" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J68" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N68" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O68" s="16"/>
       <c r="U68" s="4" t="s">
@@ -5615,27 +5625,27 @@
         <v>225</v>
       </c>
       <c r="I69" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J69" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="L69" s="5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="M69" s="5"/>
       <c r="N69" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O69" s="16"/>
       <c r="P69" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q69" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U69" t="s">
         <v>26</v>
@@ -5647,7 +5657,7 @@
         <v>51</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="70" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
@@ -5673,13 +5683,13 @@
         <v>228</v>
       </c>
       <c r="I70" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J70" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N70" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O70" s="16"/>
       <c r="U70" s="4" t="s">
@@ -5718,13 +5728,13 @@
         <v>228</v>
       </c>
       <c r="I71" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J71" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N71" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O71" s="16"/>
       <c r="U71" s="4" t="s">
@@ -5761,13 +5771,13 @@
       </c>
       <c r="H72" s="2"/>
       <c r="I72" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J72" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N72" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O72" s="16"/>
       <c r="U72" s="4" t="s">
@@ -5806,13 +5816,13 @@
         <v>236</v>
       </c>
       <c r="I73" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J73" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N73" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O73" s="16"/>
       <c r="U73" s="4" t="s">
@@ -5851,13 +5861,13 @@
         <v>240</v>
       </c>
       <c r="I74" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J74" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N74" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O74" s="16"/>
       <c r="U74" s="4" t="s">
@@ -5896,13 +5906,13 @@
         <v>244</v>
       </c>
       <c r="I75" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J75" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N75" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O75" s="16"/>
       <c r="U75" s="4" t="s">
@@ -5942,13 +5952,13 @@
       </c>
       <c r="H76" s="2"/>
       <c r="I76" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J76" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N76" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O76" s="16"/>
       <c r="S76" s="2"/>
@@ -5989,13 +5999,13 @@
         <v>251</v>
       </c>
       <c r="I77" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J77" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N77" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O77" s="16"/>
       <c r="U77" s="4" t="s">
@@ -6034,13 +6044,13 @@
         <v>255</v>
       </c>
       <c r="I78" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J78" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N78" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O78" s="16"/>
       <c r="U78" s="4" t="s">
@@ -6079,13 +6089,13 @@
         <v>258</v>
       </c>
       <c r="I79" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J79" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N79" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O79" s="16"/>
       <c r="U79" s="4" t="s">
@@ -6124,27 +6134,27 @@
         <v>175</v>
       </c>
       <c r="I80" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J80" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="K80" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M80" s="5"/>
       <c r="N80" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O80" s="16"/>
       <c r="P80" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q80" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="S80" s="2"/>
       <c r="U80" t="s">
@@ -6157,10 +6167,10 @@
         <v>51</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="Y80" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="81" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
@@ -6186,27 +6196,27 @@
         <v>175</v>
       </c>
       <c r="I81" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J81" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="K81" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="L81" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M81" s="5"/>
       <c r="N81" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O81" s="16"/>
       <c r="P81" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q81" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U81" t="s">
         <v>26</v>
@@ -6218,7 +6228,7 @@
         <v>51</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
     </row>
     <row r="82" spans="1:25" ht="409.5" x14ac:dyDescent="0.45">
@@ -6244,27 +6254,27 @@
         <v>175</v>
       </c>
       <c r="I82" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="L82" s="5" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="M82" s="5"/>
       <c r="N82" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O82" s="16"/>
       <c r="P82" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="Q82" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="S82" s="2"/>
       <c r="U82" t="s">
@@ -6277,10 +6287,10 @@
         <v>38</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="83" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -6303,13 +6313,13 @@
         <v>50</v>
       </c>
       <c r="I83" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N83" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O83" s="16"/>
       <c r="U83" s="4" t="s">
@@ -6348,15 +6358,15 @@
         <v>274</v>
       </c>
       <c r="I84" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
       <c r="N84" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O84" s="16"/>
       <c r="U84" s="4" t="s">

--- a/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17bc974f5891b333/Documents/ProPASS/Harmo/NHATS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="259" documentId="8_{5005C4B8-8269-4712-9267-05709C8265AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{339FDDB2-46A3-461B-A141-A096D22A068A}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="8_{5005C4B8-8269-4712-9267-05709C8265AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3C1AF40-C97F-4DEB-8AE0-57A346E08889}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F744FAC3-0BAB-4C7A-92B3-0824573F48DB}"/>
   </bookViews>
@@ -1270,10 +1270,6 @@
     <t>dt12getoplcs1; ha12howgtstr7</t>
   </si>
   <si>
-    <t xml:space="preserve">r12dintvwrage
-</t>
-  </si>
-  <si>
     <t>R12 AB COVER DATE MONTH;
 R12 AB COVER DATE YEAR</t>
   </si>
@@ -1636,6 +1632,9 @@
 dt12getoplcs1 == 2 &amp; ha12howgtstr7 == 2 ~ 0;
 TRUE ~ NA_integer_
 )</t>
+  </si>
+  <si>
+    <t>r12dintvwrage</t>
   </si>
 </sst>
 </file>
@@ -2173,7 +2172,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>3</v>
@@ -2182,10 +2181,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>367</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>368</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>1</v>
@@ -2197,10 +2196,10 @@
         <v>275</v>
       </c>
       <c r="L1" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="M1" s="10" t="s">
         <v>369</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>370</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>277</v>
@@ -2215,7 +2214,7 @@
         <v>280</v>
       </c>
       <c r="R1" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="S1" s="14" t="s">
         <v>9</v>
@@ -2259,7 +2258,7 @@
         <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J2" t="s">
         <v>284</v>
@@ -2279,7 +2278,7 @@
         <v>311</v>
       </c>
       <c r="Q2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R2" s="16"/>
       <c r="S2" s="4"/>
@@ -2290,7 +2289,7 @@
         <v>27</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="X2" s="4" t="s">
         <v>284</v>
@@ -2317,7 +2316,7 @@
         <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J3" t="s">
         <v>292</v>
@@ -2328,7 +2327,7 @@
       </c>
       <c r="O3" s="16"/>
       <c r="Q3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
@@ -2370,13 +2369,13 @@
       </c>
       <c r="H4" s="2"/>
       <c r="I4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>316</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -2399,7 +2398,7 @@
         <v>14</v>
       </c>
       <c r="Y4" s="11" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
@@ -2425,13 +2424,13 @@
         <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="K5" t="s">
         <v>400</v>
-      </c>
-      <c r="K5" t="s">
-        <v>401</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>286</v>
@@ -2445,7 +2444,7 @@
         <v>311</v>
       </c>
       <c r="Q5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U5" t="s">
         <v>26</v>
@@ -2484,13 +2483,13 @@
       </c>
       <c r="H6" s="2"/>
       <c r="I6" t="s">
-        <v>378</v>
-      </c>
-      <c r="J6" t="s">
-        <v>336</v>
+        <v>377</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>404</v>
       </c>
       <c r="K6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
@@ -2504,7 +2503,7 @@
         <v>311</v>
       </c>
       <c r="Q6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R6" t="s">
         <v>32</v>
@@ -2545,7 +2544,7 @@
         <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J7" t="s">
         <v>292</v>
@@ -2596,13 +2595,13 @@
         <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J8" t="s">
         <v>317</v>
       </c>
       <c r="K8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>291</v>
@@ -2616,7 +2615,7 @@
         <v>311</v>
       </c>
       <c r="Q8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U8" t="s">
         <v>26</v>
@@ -2654,13 +2653,13 @@
         <v>46</v>
       </c>
       <c r="I9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J9" t="s">
         <v>318</v>
       </c>
       <c r="K9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>302</v>
@@ -2674,7 +2673,7 @@
         <v>311</v>
       </c>
       <c r="Q9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U9" s="4" t="s">
         <v>26</v>
@@ -2686,7 +2685,7 @@
         <v>51</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -2709,13 +2708,13 @@
         <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J10" t="s">
         <v>319</v>
       </c>
       <c r="K10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N10" t="s">
         <v>315</v>
@@ -2725,7 +2724,7 @@
         <v>311</v>
       </c>
       <c r="Q10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R10" t="s">
         <v>293</v>
@@ -2763,13 +2762,13 @@
         <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J11" t="s">
+        <v>373</v>
+      </c>
+      <c r="K11" t="s">
         <v>374</v>
-      </c>
-      <c r="K11" t="s">
-        <v>375</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>13</v>
@@ -2782,7 +2781,7 @@
         <v>311</v>
       </c>
       <c r="Q11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U11" t="s">
         <v>26</v>
@@ -2820,13 +2819,13 @@
         <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J12" t="s">
         <v>317</v>
       </c>
       <c r="K12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L12" t="s">
         <v>291</v>
@@ -2840,7 +2839,7 @@
         <v>311</v>
       </c>
       <c r="Q12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U12" t="s">
         <v>26</v>
@@ -2852,7 +2851,7 @@
         <v>38</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="171" x14ac:dyDescent="0.45">
@@ -2878,13 +2877,13 @@
         <v>62</v>
       </c>
       <c r="I13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J13" t="s">
         <v>320</v>
       </c>
       <c r="K13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>294</v>
@@ -2933,13 +2932,13 @@
         <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J14" t="s">
         <v>320</v>
       </c>
       <c r="K14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>294</v>
@@ -2953,7 +2952,7 @@
         <v>311</v>
       </c>
       <c r="Q14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U14" t="s">
         <v>26</v>
@@ -2965,7 +2964,7 @@
         <v>38</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -2991,16 +2990,16 @@
         <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J15" t="s">
+        <v>385</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="L15" s="5" t="s">
         <v>386</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>387</v>
       </c>
       <c r="N15" t="s">
         <v>315</v>
@@ -3010,7 +3009,7 @@
         <v>311</v>
       </c>
       <c r="Q15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U15" s="4" t="s">
         <v>14</v>
@@ -3025,7 +3024,7 @@
         <v>14</v>
       </c>
       <c r="Y15" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
@@ -3052,13 +3051,13 @@
       </c>
       <c r="H16" s="2"/>
       <c r="I16" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>321</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>297</v>
@@ -3071,7 +3070,7 @@
         <v>311</v>
       </c>
       <c r="Q16" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R16" t="s">
         <v>296</v>
@@ -3086,7 +3085,7 @@
         <v>75</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
@@ -3112,7 +3111,7 @@
         <v>78</v>
       </c>
       <c r="I17" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J17" t="s">
         <v>292</v>
@@ -3125,7 +3124,7 @@
         <v>311</v>
       </c>
       <c r="Q17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U17" s="4" t="s">
         <v>26</v>
@@ -3164,13 +3163,13 @@
       </c>
       <c r="H18" s="2"/>
       <c r="I18" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J18" t="s">
         <v>322</v>
       </c>
       <c r="K18" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N18" t="s">
         <v>315</v>
@@ -3180,7 +3179,7 @@
         <v>311</v>
       </c>
       <c r="Q18" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R18" t="s">
         <v>82</v>
@@ -3195,7 +3194,7 @@
         <v>75</v>
       </c>
       <c r="X18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
@@ -3221,7 +3220,7 @@
         <v>78</v>
       </c>
       <c r="I19" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J19" t="s">
         <v>292</v>
@@ -3234,7 +3233,7 @@
         <v>311</v>
       </c>
       <c r="Q19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U19" s="4" t="s">
         <v>26</v>
@@ -3272,13 +3271,13 @@
         <v>87</v>
       </c>
       <c r="I20" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>323</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N20" t="s">
         <v>315</v>
@@ -3288,7 +3287,7 @@
         <v>311</v>
       </c>
       <c r="Q20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R20" t="s">
         <v>299</v>
@@ -3303,7 +3302,7 @@
         <v>51</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
@@ -3330,13 +3329,13 @@
       </c>
       <c r="H21" s="2"/>
       <c r="I21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J21" t="s">
         <v>324</v>
       </c>
       <c r="K21" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="N21" t="s">
         <v>315</v>
@@ -3346,7 +3345,7 @@
         <v>311</v>
       </c>
       <c r="Q21" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R21" t="s">
         <v>74</v>
@@ -3361,7 +3360,7 @@
         <v>75</v>
       </c>
       <c r="X21" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="57" x14ac:dyDescent="0.45">
@@ -3387,13 +3386,13 @@
         <v>78</v>
       </c>
       <c r="I22" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J22" t="s">
         <v>325</v>
       </c>
       <c r="K22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>300</v>
@@ -3407,7 +3406,7 @@
         <v>311</v>
       </c>
       <c r="Q22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U22" t="s">
         <v>26</v>
@@ -3445,7 +3444,7 @@
         <v>94</v>
       </c>
       <c r="I23" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J23" t="s">
         <v>292</v>
@@ -3478,7 +3477,7 @@
         <v>13</v>
       </c>
       <c r="I24" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J24" t="s">
         <v>292</v>
@@ -3523,7 +3522,7 @@
         <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J25" t="s">
         <v>292</v>
@@ -3568,7 +3567,7 @@
         <v>100</v>
       </c>
       <c r="I26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J26" t="s">
         <v>292</v>
@@ -3613,7 +3612,7 @@
         <v>106</v>
       </c>
       <c r="I27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J27" t="s">
         <v>292</v>
@@ -3659,7 +3658,7 @@
       </c>
       <c r="H28" s="2"/>
       <c r="I28" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J28" t="s">
         <v>292</v>
@@ -3704,7 +3703,7 @@
         <v>112</v>
       </c>
       <c r="I29" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J29" t="s">
         <v>292</v>
@@ -3749,7 +3748,7 @@
         <v>115</v>
       </c>
       <c r="I30" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J30" t="s">
         <v>292</v>
@@ -3794,7 +3793,7 @@
         <v>118</v>
       </c>
       <c r="I31" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J31" t="s">
         <v>292</v>
@@ -3839,7 +3838,7 @@
         <v>121</v>
       </c>
       <c r="I32" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J32" t="s">
         <v>292</v>
@@ -3884,7 +3883,7 @@
         <v>121</v>
       </c>
       <c r="I33" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J33" t="s">
         <v>292</v>
@@ -3929,7 +3928,7 @@
         <v>121</v>
       </c>
       <c r="I34" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J34" t="s">
         <v>292</v>
@@ -3974,7 +3973,7 @@
         <v>121</v>
       </c>
       <c r="I35" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J35" t="s">
         <v>292</v>
@@ -4019,7 +4018,7 @@
         <v>121</v>
       </c>
       <c r="I36" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J36" t="s">
         <v>292</v>
@@ -4064,7 +4063,7 @@
         <v>132</v>
       </c>
       <c r="I37" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J37" t="s">
         <v>292</v>
@@ -4110,7 +4109,7 @@
       </c>
       <c r="H38" s="2"/>
       <c r="I38" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J38" t="s">
         <v>292</v>
@@ -4155,7 +4154,7 @@
         <v>140</v>
       </c>
       <c r="I39" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J39" t="s">
         <v>292</v>
@@ -4207,7 +4206,7 @@
       </c>
       <c r="H40" s="2"/>
       <c r="I40" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J40" t="s">
         <v>292</v>
@@ -4252,7 +4251,7 @@
         <v>140</v>
       </c>
       <c r="I41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J41" t="s">
         <v>292</v>
@@ -4297,7 +4296,7 @@
         <v>149</v>
       </c>
       <c r="I42" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J42" t="s">
         <v>292</v>
@@ -4343,7 +4342,7 @@
       </c>
       <c r="H43" s="2"/>
       <c r="I43" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J43" t="s">
         <v>292</v>
@@ -4388,7 +4387,7 @@
         <v>156</v>
       </c>
       <c r="I44" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J44" t="s">
         <v>292</v>
@@ -4433,13 +4432,13 @@
         <v>160</v>
       </c>
       <c r="I45" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J45" t="s">
         <v>326</v>
       </c>
       <c r="K45" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>302</v>
@@ -4489,7 +4488,7 @@
         <v>163</v>
       </c>
       <c r="I46" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J46" t="s">
         <v>327</v>
@@ -4542,13 +4541,13 @@
       </c>
       <c r="H47" s="2"/>
       <c r="I47" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J47" t="s">
         <v>327</v>
       </c>
       <c r="K47" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>165</v>
@@ -4562,7 +4561,7 @@
         <v>311</v>
       </c>
       <c r="Q47" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U47" t="s">
         <v>26</v>
@@ -4574,7 +4573,7 @@
         <v>51</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
@@ -4600,13 +4599,13 @@
         <v>171</v>
       </c>
       <c r="I48" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J48" t="s">
         <v>328</v>
       </c>
       <c r="K48" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>305</v>
@@ -4620,7 +4619,7 @@
         <v>311</v>
       </c>
       <c r="Q48" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U48" t="s">
         <v>26</v>
@@ -4632,10 +4631,10 @@
         <v>38</v>
       </c>
       <c r="X48" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Y48" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" spans="1:25" ht="213.75" x14ac:dyDescent="0.45">
@@ -4661,13 +4660,13 @@
         <v>175</v>
       </c>
       <c r="I49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J49" t="s">
         <v>329</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>306</v>
@@ -4681,7 +4680,7 @@
         <v>311</v>
       </c>
       <c r="Q49" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="S49" s="2"/>
       <c r="U49" t="s">
@@ -4694,10 +4693,10 @@
         <v>51</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" spans="1:25" ht="213.75" x14ac:dyDescent="0.45">
@@ -4723,13 +4722,13 @@
         <v>175</v>
       </c>
       <c r="I50" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J50" t="s">
         <v>330</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>306</v>
@@ -4743,7 +4742,7 @@
         <v>311</v>
       </c>
       <c r="Q50" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="S50" s="2"/>
       <c r="U50" t="s">
@@ -4756,10 +4755,10 @@
         <v>51</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
@@ -4785,13 +4784,13 @@
         <v>175</v>
       </c>
       <c r="I51" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J51" t="s">
         <v>331</v>
       </c>
       <c r="K51" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>182</v>
@@ -4805,7 +4804,7 @@
         <v>311</v>
       </c>
       <c r="Q51" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U51" t="s">
         <v>26</v>
@@ -4817,7 +4816,7 @@
         <v>51</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="52" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
@@ -4843,7 +4842,7 @@
         <v>186</v>
       </c>
       <c r="I52" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J52" t="s">
         <v>292</v>
@@ -4890,13 +4889,13 @@
         <v>175</v>
       </c>
       <c r="I53" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>332</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>307</v>
@@ -4910,7 +4909,7 @@
         <v>311</v>
       </c>
       <c r="Q53" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U53" t="s">
         <v>26</v>
@@ -4922,7 +4921,7 @@
         <v>51</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="54" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -4948,7 +4947,7 @@
         <v>175</v>
       </c>
       <c r="I54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J54" t="s">
         <v>292</v>
@@ -4993,7 +4992,7 @@
         <v>175</v>
       </c>
       <c r="I55" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J55" t="s">
         <v>292</v>
@@ -5040,7 +5039,7 @@
         <v>175</v>
       </c>
       <c r="I56" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J56" t="s">
         <v>292</v>
@@ -5087,7 +5086,7 @@
         <v>175</v>
       </c>
       <c r="I57" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J57" t="s">
         <v>292</v>
@@ -5132,7 +5131,7 @@
         <v>175</v>
       </c>
       <c r="I58" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J58" t="s">
         <v>292</v>
@@ -5174,7 +5173,7 @@
         <v>16</v>
       </c>
       <c r="I59" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J59" t="s">
         <v>292</v>
@@ -5216,7 +5215,7 @@
         <v>16</v>
       </c>
       <c r="I60" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J60" t="s">
         <v>292</v>
@@ -5258,7 +5257,7 @@
         <v>16</v>
       </c>
       <c r="I61" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J61" t="s">
         <v>292</v>
@@ -5300,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="I62" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J62" t="s">
         <v>292</v>
@@ -5342,7 +5341,7 @@
         <v>16</v>
       </c>
       <c r="I63" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J63" t="s">
         <v>292</v>
@@ -5386,7 +5385,7 @@
         <v>16</v>
       </c>
       <c r="I64" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J64" t="s">
         <v>292</v>
@@ -5429,7 +5428,7 @@
       </c>
       <c r="H65" s="2"/>
       <c r="I65" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J65" t="s">
         <v>292</v>
@@ -5474,16 +5473,16 @@
         <v>216</v>
       </c>
       <c r="I66" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J66" t="s">
         <v>333</v>
       </c>
       <c r="K66" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M66" s="5"/>
       <c r="N66" t="s">
@@ -5494,7 +5493,7 @@
         <v>311</v>
       </c>
       <c r="Q66" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="S66" s="2"/>
       <c r="U66" t="s">
@@ -5507,7 +5506,7 @@
         <v>38</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Y66" s="2"/>
     </row>
@@ -5535,7 +5534,7 @@
       </c>
       <c r="H67" s="2"/>
       <c r="I67" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J67" t="s">
         <v>292</v>
@@ -5580,7 +5579,7 @@
         <v>222</v>
       </c>
       <c r="I68" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J68" t="s">
         <v>292</v>
@@ -5625,13 +5624,13 @@
         <v>225</v>
       </c>
       <c r="I69" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J69" t="s">
         <v>334</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>308</v>
@@ -5645,7 +5644,7 @@
         <v>311</v>
       </c>
       <c r="Q69" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U69" t="s">
         <v>26</v>
@@ -5657,7 +5656,7 @@
         <v>51</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="70" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
@@ -5683,7 +5682,7 @@
         <v>228</v>
       </c>
       <c r="I70" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J70" t="s">
         <v>292</v>
@@ -5728,7 +5727,7 @@
         <v>228</v>
       </c>
       <c r="I71" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J71" t="s">
         <v>292</v>
@@ -5771,7 +5770,7 @@
       </c>
       <c r="H72" s="2"/>
       <c r="I72" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J72" t="s">
         <v>292</v>
@@ -5816,7 +5815,7 @@
         <v>236</v>
       </c>
       <c r="I73" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J73" t="s">
         <v>292</v>
@@ -5861,7 +5860,7 @@
         <v>240</v>
       </c>
       <c r="I74" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J74" t="s">
         <v>292</v>
@@ -5906,7 +5905,7 @@
         <v>244</v>
       </c>
       <c r="I75" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J75" t="s">
         <v>292</v>
@@ -5952,7 +5951,7 @@
       </c>
       <c r="H76" s="2"/>
       <c r="I76" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J76" t="s">
         <v>292</v>
@@ -5999,7 +5998,7 @@
         <v>251</v>
       </c>
       <c r="I77" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J77" t="s">
         <v>292</v>
@@ -6044,7 +6043,7 @@
         <v>255</v>
       </c>
       <c r="I78" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J78" t="s">
         <v>292</v>
@@ -6089,7 +6088,7 @@
         <v>258</v>
       </c>
       <c r="I79" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J79" t="s">
         <v>292</v>
@@ -6134,13 +6133,13 @@
         <v>175</v>
       </c>
       <c r="I80" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J80" t="s">
+        <v>388</v>
+      </c>
+      <c r="K80" t="s">
         <v>389</v>
-      </c>
-      <c r="K80" t="s">
-        <v>390</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>310</v>
@@ -6154,7 +6153,7 @@
         <v>311</v>
       </c>
       <c r="Q80" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="S80" s="2"/>
       <c r="U80" t="s">
@@ -6167,10 +6166,10 @@
         <v>51</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Y80" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="81" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
@@ -6196,13 +6195,13 @@
         <v>175</v>
       </c>
       <c r="I81" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J81" t="s">
         <v>335</v>
       </c>
       <c r="K81" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L81" s="5" t="s">
         <v>309</v>
@@ -6216,7 +6215,7 @@
         <v>311</v>
       </c>
       <c r="Q81" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U81" t="s">
         <v>26</v>
@@ -6228,7 +6227,7 @@
         <v>51</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="82" spans="1:25" ht="409.5" x14ac:dyDescent="0.45">
@@ -6254,16 +6253,16 @@
         <v>175</v>
       </c>
       <c r="I82" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J82" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="K82" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="K82" s="2" t="s">
+      <c r="L82" s="5" t="s">
         <v>394</v>
-      </c>
-      <c r="L82" s="5" t="s">
-        <v>395</v>
       </c>
       <c r="M82" s="5"/>
       <c r="N82" t="s">
@@ -6274,7 +6273,7 @@
         <v>311</v>
       </c>
       <c r="Q82" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="S82" s="2"/>
       <c r="U82" t="s">
@@ -6287,10 +6286,10 @@
         <v>38</v>
       </c>
       <c r="X82" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="Y82" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="Y82" s="2" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="83" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -6313,7 +6312,7 @@
         <v>50</v>
       </c>
       <c r="I83" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>292</v>
@@ -6358,7 +6357,7 @@
         <v>274</v>
       </c>
       <c r="I84" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>292</v>

--- a/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17bc974f5891b333/Documents/ProPASS/Harmo/NHATS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="263" documentId="8_{5005C4B8-8269-4712-9267-05709C8265AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3C1AF40-C97F-4DEB-8AE0-57A346E08889}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="8_{B04BC2F6-0886-423B-9CF8-2AF8452D03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEE8A9EB-BF23-4F9D-9D09-C606FCA899DC}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F744FAC3-0BAB-4C7A-92B3-0824573F48DB}"/>
+    <workbookView xWindow="71880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F744FAC3-0BAB-4C7A-92B3-0824573F48DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="400">
   <si>
     <t>index</t>
   </si>
@@ -556,9 +556,6 @@
   <si>
     <t>1 = Occasionaly ;
 2 = Daily/Almost daily</t>
-  </si>
-  <si>
-    <t>R14 SD3 NUM OF CIGARETTES PER DAY</t>
   </si>
   <si>
     <t>-9 = Missing;
@@ -1004,6 +1001,9 @@
     <t>hrs/week</t>
   </si>
   <si>
+    <t>recode (3 = 1; c(1,2) = 0; c(-9,-8,-7,-1) = NA; ELSE = NA)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 = Married; 
 2 = Living with a partner;
 3 = Separated;
@@ -1017,6 +1017,9 @@
 </t>
   </si>
   <si>
+    <t>recode (c(1,2) = 1; c(3,4,5,6) = 0; c(-9,-8,-7) = NA; -1 = NA; ELSE = NA)</t>
+  </si>
+  <si>
     <t>“Living with a partner” does not imply ever married. Since this category cannot be classified with certainty into the DataSchema categories, the variable is considered incompatible.</t>
   </si>
   <si>
@@ -1065,6 +1068,9 @@
 3 = Good;
 4 = Fair;
 5 = Poor</t>
+  </si>
+  <si>
+    <t>recode (5 = 1; 4 = 2; 3 = 3; c(1,2) = 4; ELSE = NA)</t>
   </si>
   <si>
     <t xml:space="preserve">-7 = DF;
@@ -1083,6 +1089,9 @@
 </t>
   </si>
   <si>
+    <t>the study does not include an “other” category, therefor "No" category cannot be produced.</t>
+  </si>
+  <si>
     <t>-9 = Missing; 
 -7 = RF;
 -8 = DK; 
@@ -1090,6 +1099,9 @@
 1 = YES;
 2 = NO
 7 = PREVIOUSLY REPORTED</t>
+  </si>
+  <si>
+    <t>recode (c(1,7) = 1; 2 = 0; c(-9,-8,-7) = NA; -1 = NA; ELSE = NA)</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1113,6 +1125,340 @@
 </t>
   </si>
   <si>
+    <t>case_when(
+dt11getoplcs1 == 1 | ha11howgtstr7 == 1 ~ 1;
+dt11getoplcs1 == 2 &amp; ha11howgtstr7 == 2 ~ 0;
+TRUE ~ NA_integer
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questionnaire </t>
+  </si>
+  <si>
+    <t>JSN Comment/Question</t>
+  </si>
+  <si>
+    <t>adm_wave</t>
+  </si>
+  <si>
+    <t>Wave number</t>
+  </si>
+  <si>
+    <t>dataschema_variable_label</t>
+  </si>
+  <si>
+    <t>unit/other_format</t>
+  </si>
+  <si>
+    <t>Categories::label</t>
+  </si>
+  <si>
+    <t>categories/format</t>
+  </si>
+  <si>
+    <t>field_type</t>
+  </si>
+  <si>
+    <t>input_keywords</t>
+  </si>
+  <si>
+    <t>id_creation</t>
+  </si>
+  <si>
+    <t>only the date of the activites booklet is completed and this is not necessairly the same date that the general questionnaire is completed.</t>
+  </si>
+  <si>
+    <t>Codes 1–3 are unambiguously urban (metro areas) and codes 8–9 are unambiguously rural. However, codes 4–7 represent intermediate non-metro areas that could reasonably be classified as either urban or rural. Decision needed on cutpoint for rural vs urban</t>
+  </si>
+  <si>
+    <t>ab13datemonth;
+ab13dateyear</t>
+  </si>
+  <si>
+    <t>R13 AB COVER DATE MONTH;
+R13 AB COVER DATE YEAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">r13dintvwrage
+</t>
+  </si>
+  <si>
+    <t>R13 D AGE OF SP AT INTERVIEW</t>
+  </si>
+  <si>
+    <t>lf13workfpay</t>
+  </si>
+  <si>
+    <t>R13 LF1 WORKED FOR PAY RECENTLY</t>
+  </si>
+  <si>
+    <t>lf13wrkplstmn;lf13hrswkwork</t>
+  </si>
+  <si>
+    <t>R13 LF3 WORK FOR PAY IN LST MONTH; R13 LF5 HRS PR WEEK WORK MAIN JOB</t>
+  </si>
+  <si>
+    <t>lf13hrswkwork</t>
+  </si>
+  <si>
+    <t>R13 LF5 HRS PR WEEK WORK MAIN JOB</t>
+  </si>
+  <si>
+    <t>lf13doccup</t>
+  </si>
+  <si>
+    <t>R13 D CURRENT OCCUPATION CATEGORY</t>
+  </si>
+  <si>
+    <t>hh13dmarstat</t>
+  </si>
+  <si>
+    <t>R13 D MARITAL STATUS AT R13</t>
+  </si>
+  <si>
+    <t>r13drucc</t>
+  </si>
+  <si>
+    <t>R13 D METRO / NON-METRO RESIDENCE</t>
+  </si>
+  <si>
+    <t>hw13howtallft;
+hw13howtallin</t>
+  </si>
+  <si>
+    <t>R13 HW7 HOW TALL ARE YOU FEET;
+R13 HW8 HOW TALL ARE YOU INCHES</t>
+  </si>
+  <si>
+    <t>hw13currweigh</t>
+  </si>
+  <si>
+    <t>R13 HW2 YOU CURRENTLY WEIGH</t>
+  </si>
+  <si>
+    <t>hw13howtallft;
+hw13howtallin; 
+hw13currweigh</t>
+  </si>
+  <si>
+    <t>R13 HW7 HOW TALL ARE YOU FEET;
+R13 HW8 HOW TALL ARE YOU INCHES;
+R13 HW2 YOU CURRENTLY WEIGH</t>
+  </si>
+  <si>
+    <t>wc13wstmsrinc</t>
+  </si>
+  <si>
+    <t>R13 WC4A WAIST MEASURE INCHES</t>
+  </si>
+  <si>
+    <t>wc13whomeasur</t>
+  </si>
+  <si>
+    <t>R13 WC6 WHO MEASURED</t>
+  </si>
+  <si>
+    <t>sd13smokesnow</t>
+  </si>
+  <si>
+    <t>R13 SD2 SMOKES NOW</t>
+  </si>
+  <si>
+    <t>sd13numcigday</t>
+  </si>
+  <si>
+    <t>R13 SD3 NUM OF CIGARETTES PER DAY</t>
+  </si>
+  <si>
+    <t>hc13health</t>
+  </si>
+  <si>
+    <t>R13 HC1 OVERALL HEALTH CONDITION</t>
+  </si>
+  <si>
+    <t>hc13disescn1; hc13disescn2</t>
+  </si>
+  <si>
+    <t>R13 HC2 SP HAD HEART ATTACK; R13 HC2 SP HAS HEART DISEASE INCLUDES EVER</t>
+  </si>
+  <si>
+    <t>hc13disescn4; hc13disescn5</t>
+  </si>
+  <si>
+    <t>R13 HC2 SP HAS ARTHRITIS INCLUDES EVER;  R13 HC2 SP HAS OSTEOPOROSIS INCLUDES EVER</t>
+  </si>
+  <si>
+    <t>hc13disescn6</t>
+  </si>
+  <si>
+    <t>R13 HC2 SP HAS DIABETES INCLUDES EVER</t>
+  </si>
+  <si>
+    <t>hc13disescn10; hc13cancerty2;
+hc13cancerty3;
+hc13cancerty4;
+hc13cancerty5;
+hc13cancerty6;
+hc13cancerty7;
+hc13cancerty8;
+hc13cancerty1</t>
+  </si>
+  <si>
+    <t>R13 HC2 SP HAS CANCER;
+R13 HC3 SP HAD BREAST CANCER;
+R13 HC3 SP HAD PROSTATE CANCER;
+R13 HC3 SP HAD BLADDER CANCER;
+R13 HC3 SP HAD CRV OVRN UTRN CNCR;
+R13 HC3 SP HAD COLON CANCER;
+R13 HC3 SP HAD KIDNEY CANCER;
+R13 HC3 SP HAD OTHER CANCER;
+R13 HC3 SP HAD SKIN CANCER</t>
+  </si>
+  <si>
+    <t>hc13disescn9</t>
+  </si>
+  <si>
+    <t>R13 HC2 SP HAS DEMENTIA OR ALZH INCLUDES EVER</t>
+  </si>
+  <si>
+    <t>hc13trbfalbck; hc13aslep30mn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TROBLE FALLNG BCK ASLEEP; R13 HC20 OVER 30 MIN FALL ASLEEP </t>
+  </si>
+  <si>
+    <t>dt13getoplcs1; ha13howgtstr7</t>
+  </si>
+  <si>
+    <t>R13 DT4A SP WALKED GOT PLACES; R13 HA23 SP WALKED TO THE STORE</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>participant</t>
+  </si>
+  <si>
+    <t>study</t>
+  </si>
+  <si>
+    <t>case_when(
+  lf13wrkplstmn != 1 ~ NA_integer_,
+  lf13hrswkwork &gt;= 35 ~ 2L,
+  lf13hrswkwork &gt; 0 &amp; lf13hrswkwork &lt; 35 ~ 1L,
+  lf13hrswkwork %in% c(-7, -8, -9, -1) ~ NA_integer_,
+  TRUE ~ NA_integer_
+)</t>
+  </si>
+  <si>
+    <t>case_when(
+  hw13howtallft %in% c(-7, -8, -9, -1) | 
+  hw13howtallin %in% c(-7, -8, -9, -1) ~ NA_real_,
+  !is.na(hw13howtallft) &amp; !is.na(hw13howtallin) ~ 
+    ((hw13howtallft * 12) + hw13howtallin) * 2.54,
+  TRUE ~ NA_real_
+)</t>
+  </si>
+  <si>
+    <t>hw13currweigh * 0.45359237</t>
+  </si>
+  <si>
+    <t>case_when(
+  hw13howtallft %in% c(-7, -8, -9, -1) |
+  hw13howtallin %in% c(-7, -8, -9, -1) |
+  hw13currweigh %in% c(-7, -8, -9, -1) ~ NA_real_,
+  !is.na(hw13howtallft) &amp; !is.na(hw13howtallin) &amp; !is.na(hw13currweigh) ~ {
+    height_m &lt;- ((hw13howtallft * 12) + hw13howtallin) * 0.0254
+    weight_kg &lt;- hw13currweigh * 0.453592
+    weight_kg / (height_m^2)
+  },
+  TRUE ~ NA_real_
+)</t>
+  </si>
+  <si>
+    <t>wc13wstmsrinc * 2.54</t>
+  </si>
+  <si>
+    <t>case_when(
+sd13numcigday %in% c(-9,-8,-7,-1,999) ~ NA_real_;
+TRUE ~ sd13numcigday * 7
+)</t>
+  </si>
+  <si>
+    <t>case_when(
+hc13disescn1 %in% c(1,7) | hc13disescn2 %in% c(1,7) ~ 1;
+TRUE ~ NA
+)</t>
+  </si>
+  <si>
+    <t>case_when(
+hc13disescn4 %in% c(1,7) | hc13disescn5 %in% c(1,7) ~ 1;
+TRUE ~ NA
+)</t>
+  </si>
+  <si>
+    <t>case_when(
+hc13disescn6 %in% c(1,7) ~ 1;
+TRUE ~ NA
+)</t>
+  </si>
+  <si>
+    <t>case_when(
+hc13cancerty2 %in% c(1,7) | 
+hc13cancerty3 %in% c(1,7) | 
+hc13cancerty4 %in% c(1,7) | 
+hc13cancerty5 %in% c(1,7) | 
+hc13cancerty6 %in% c(1,7) | 
+hc13cancerty7 %in% c(1,7) | 
+hc13cancerty8 %in% c(1,7) ~ 1;
+hc13cancerty2 == 2 &amp; 
+hc13cancerty3 == 2 &amp; 
+hc13cancerty4 == 2 &amp; 
+hc13cancerty5 == 2 &amp; 
+hc13cancerty6 == 2 &amp; 
+hc13cancerty7 == 2 &amp; 
+hc13cancerty8 == 2 ~ 0;
+TRUE ~ NA_integer
+)</t>
+  </si>
+  <si>
+    <t>case_when(
+hc13trbfalbck %in% c(1,2,3) | hc13aslep30mn %in% c(1,2,3) ~ 1;
+hc13trbfalbck %in% c(4,7) &amp; hc13aslep30mn %in% c(4,5) ~ 0;
+TRUE ~ NA_integer
+)</t>
+  </si>
+  <si>
+    <t>NHATS_R13_Final_Release_SAS; NHATS_R13_SP_Sen_Dem_STATA</t>
+  </si>
+  <si>
+    <t>undetermined</t>
+  </si>
+  <si>
+    <t>r13dgender</t>
+  </si>
+  <si>
+    <t>R13 D GENDER OF SP</t>
+  </si>
+  <si>
+    <t>we don’t have access to sensitive data? As only skin cancer and general cancer declaration is given in the SP public file. To clarify</t>
+  </si>
+  <si>
+    <t>pa13dfavact</t>
+  </si>
+  <si>
+    <t>R13 D FAVORITE ACTIVITY AT R13</t>
+  </si>
+  <si>
+    <t>pa13dfavact is in text format, would be difficult to read through open text to fetch physical activity based leisure activities.</t>
+  </si>
+  <si>
+    <t>pa13vigoractv</t>
+  </si>
+  <si>
+    <t>R13 PA24 EVER VIGOROUS ACTIVITIES</t>
+  </si>
+  <si>
     <t xml:space="preserve">-9 = Missing; 
 -7 = RF;
 -8 = DK; 
@@ -1120,521 +1466,20 @@
 1 = YES;
 2 = NO
 7 = PREVIOUSLY REPORTED
--1 = Inapplicable
--8 = Don't know
--9 = Missing
-111 = Sleeping/Napping
-131 = Eating
-132 = Going out to eat
-199 = Other self-care activities
-211 = Work and work-related activities
-221 = Other income-generating activities
-241 = Volunteering
-299 = Other productive activities
-321 = Shopping for non-durable goods
-399 = Other shopping
-411 = Food and drink preparation
-434 = Outdoor maintenance
-439 = Household chores (indoor/outdoor unspecified)
-441 = Animal and pet care
-442 = Walking/exercising pets
-449 = Other animal and pet care
-451 = Vehicle maintenance and repair
-471 = Financial management
-499 = Other household activities
-511 = Physical care and assistance to others
-599 = Other physical care
-611 = Socializing in person
-612 = Socializing on the phone
-616 = Socializing/communicating on a computer
-621 = Watching TV/movies
-631 = Puzzles/games (not computer/online)
-632 = Gambling (not online/casino)
-636 = Puzzles/games (computer/online)
-641 = Arts, crafts, hobbies
-642 = Reading
-643 = Writing
-644 = Listening to music
-646 = Computer/online leisure
-651 = Smoking/tobacco use
-652 = Drinking alcohol
-661 = Doing nothing/relaxing
-669 = No activity
-699 = Other non-active leisure
-711 = Playing sports
-712 = Walking/jogging
-713 = Other outdoor recreation
-714 = Attending sporting events
-715 = Other physical activity (exercise, yoga, swimming, dancing)
-718 = Watching sporting events
-721 = Attending arts (plays, concerts)
-723 = Attending movies
-724 = Attending casinos
-737 = Leisure travel
-799 = Other active leisure
-811 = Attending religious activities
-812 = Other religious/spiritual activities
-821 = Attending meetings/events
-899 = Other organizational activity
-991 = Other miscellaneous
-992 = No favorite activity
-997 = Refused
-998 = Don't know
-999 = Not codeable
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Questionnaire </t>
-  </si>
-  <si>
-    <t>JSN Comment/Question</t>
-  </si>
-  <si>
-    <t>adm_wave</t>
-  </si>
-  <si>
-    <t>Wave number</t>
-  </si>
-  <si>
-    <t>R12</t>
-  </si>
-  <si>
-    <t>ab12datemonth;
-ab12dateyear</t>
-  </si>
-  <si>
-    <t>lf12workfpay</t>
-  </si>
-  <si>
-    <t>lf12wrkplstmn;lf12hrswkwork</t>
-  </si>
-  <si>
-    <t>lf12hrswkwork</t>
-  </si>
-  <si>
-    <t>hh12dmarstat</t>
-  </si>
-  <si>
-    <t>hw12howtallft;
-hw12howtallin</t>
-  </si>
-  <si>
-    <t>hw12currweigh</t>
-  </si>
-  <si>
-    <t>hw12howtallft;
-hw12howtallin; 
-hw12currweigh</t>
-  </si>
-  <si>
-    <t>wc12wstmsrinc</t>
-  </si>
-  <si>
-    <t>wc12whomeasur</t>
-  </si>
-  <si>
-    <t>sd12smokesnow</t>
-  </si>
-  <si>
-    <t>sd12numcigday</t>
-  </si>
-  <si>
-    <t>hc12health</t>
-  </si>
-  <si>
-    <t>hc12disescn1; hc12disescn2</t>
-  </si>
-  <si>
-    <t>hc12disescn4; hc12disescn5</t>
-  </si>
-  <si>
-    <t>hc12disescn6</t>
-  </si>
-  <si>
-    <t>hc12disescn10; hc12cancerty2;
-hc12cancerty3;
-hc12cancerty4;
-hc12cancerty5;
-hc12cancerty6;
-hc12cancerty7;
-hc12cancerty8;
-hc12cancerty1</t>
-  </si>
-  <si>
-    <t>hc12disescn9</t>
-  </si>
-  <si>
-    <t>hc12trbfalbck; hc12aslep30mn</t>
-  </si>
-  <si>
-    <t>dt12getoplcs1; ha12howgtstr7</t>
-  </si>
-  <si>
-    <t>R12 AB COVER DATE MONTH;
-R12 AB COVER DATE YEAR</t>
-  </si>
-  <si>
-    <t>R12 D AGE OF SP AT INTERVIEW</t>
-  </si>
-  <si>
-    <t>R12 LF1 WORKED FOR PAY RECENTLY</t>
-  </si>
-  <si>
-    <t>R12 LF3 WORK FOR PAY IN LST MONTH; R12 LF5 HRS PR WEEK WORK MAIN JOB</t>
-  </si>
-  <si>
-    <t>R12 LF5 HRS PR WEEK WORK MAIN JOB</t>
-  </si>
-  <si>
-    <t>R12 D MARITAL STATUS AT R12</t>
-  </si>
-  <si>
-    <t>R12 HW7 HOW TALL ARE YOU FEET;
-R12 HW8 HOW TALL ARE YOU INCHES</t>
-  </si>
-  <si>
-    <t>R12 HW2 YOU CURRENTLY WEIGH</t>
-  </si>
-  <si>
-    <t>R12 HW7 HOW TALL ARE YOU FEET;
-R12 HW8 HOW TALL ARE YOU INCHES;
-R12 HW2 YOU CURRENTLY WEIGH</t>
-  </si>
-  <si>
-    <t>R12 WC4A WAIST MEASURE INCHES</t>
-  </si>
-  <si>
-    <t>R12 WC6 WHO MEASURED</t>
-  </si>
-  <si>
-    <t>R12 SD2 SMOKES NOW</t>
-  </si>
-  <si>
-    <t>R12 SD3 NUM OF CIGARETTES PER DAY</t>
-  </si>
-  <si>
-    <t>R12 HC1 OVERALL HEALTH CONDITION</t>
-  </si>
-  <si>
-    <t>R12 HC2 SP HAD HEART ATTACK; R12 HC2 SP HAS HEART DISEASE INCLUDES EVER</t>
-  </si>
-  <si>
-    <t>R12 HC2 SP HAS ARTHRITIS INCLUDES EVER;  R12 HC2 SP HAS OSTEOPOROSIS INCLUDES EVER</t>
-  </si>
-  <si>
-    <t>R12 HC2 SP HAS DIABETES INCLUDES EVER</t>
-  </si>
-  <si>
-    <t>R12 HC2 SP HAS CANCER;
-R12 HC3 SP HAD BREAST CANCER;
-R12 HC3 SP HAD PROSTATE CANCER;
-R12 HC3 SP HAD BLADDER CANCER;
-R12 HC3 SP HAD CRV OVRN UTRN CNCR;
-R12 HC3 SP HAD COLON CANCER;
-R12 HC3 SP HAD KIDNEY CANCER;
-R12 HC3 SP HAD OTHER CANCER;
-R12 HC3 SP HAD SKIN CANCER</t>
-  </si>
-  <si>
-    <t>R12 HC2 SP HAS DEMENTIA OR ALZH INCLUDES EVER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TROBLE FALLNG BCK ASLEEP; R12 HC20 OVER 30 MIN FALL ASLEEP </t>
-  </si>
-  <si>
-    <t>R12 DT4A SP WALKED GOT PLACES; R12 HA23 SP WALKED TO THE STORE</t>
-  </si>
-  <si>
-    <t>case_when(
-  lf12wrkplstmn != 1 ~ NA_integer_,
-  lf12hrswkwork &gt;= 35 ~ 2L,
-  lf12hrswkwork &gt; 0 &amp; lf12hrswkwork &lt; 35 ~ 1L,
-  lf12hrswkwork %in% c(-7, -8, -9, -1) ~ NA_integer_,
-  TRUE ~ NA_integer_
+    <t>recode(
+  pa13vigoractv,
+  `1` = 1,
+  `7` = 1,
+  `2` = 0,
+  `-9` = NA_real_,
+  `-8` = NA_real_,
+  `-7` = NA_real_,
+  `-1` = NA_real_,
+  .default = NA_real_
 )</t>
-  </si>
-  <si>
-    <t>case_when(
-  hw12howtallft %in% c(-7, -8, -9, -1) | 
-  hw12howtallin %in% c(-7, -8, -9, -1) ~ NA_real_,
-  !is.na(hw12howtallft) &amp; !is.na(hw12howtallin) ~ 
-    ((hw12howtallft * 12) + hw12howtallin) * 2.54,
-  TRUE ~ NA_real_
-)</t>
-  </si>
-  <si>
-    <t>hw12currweigh * 0.45359237</t>
-  </si>
-  <si>
-    <t>wc12wstmsrinc * 2.54</t>
-  </si>
-  <si>
-    <t>case_when(
-sd12numcigday %in% c(-9,-8,-7,-1,999) ~ NA_real_;
-TRUE ~ sd12numcigday * 7
-)</t>
-  </si>
-  <si>
-    <t>case_when(
-hc12disescn1 %in% c(1,7) | hc12disescn2 %in% c(1,7) ~ 1;
-TRUE ~ NA
-)</t>
-  </si>
-  <si>
-    <t>case_when(
-hc12disescn4 %in% c(1,7) | hc12disescn5 %in% c(1,7) ~ 1;
-TRUE ~ NA
-)</t>
-  </si>
-  <si>
-    <t>case_when(
-hc12disescn6 %in% c(1,7) ~ 1;
-TRUE ~ NA
-)</t>
-  </si>
-  <si>
-    <t>dataschema_variable_label</t>
-  </si>
-  <si>
-    <t>unit/other_format</t>
-  </si>
-  <si>
-    <t>Categories::label</t>
-  </si>
-  <si>
-    <t>categories/format</t>
-  </si>
-  <si>
-    <t>field_type</t>
-  </si>
-  <si>
-    <t>input_keywords</t>
-  </si>
-  <si>
-    <t>id_creation</t>
-  </si>
-  <si>
-    <t>R12 D METRO / NON-METRO RESIDENCE</t>
-  </si>
-  <si>
-    <t>lf12doccup</t>
-  </si>
-  <si>
-    <t>R12 D CURRENT OCCUPATION CATEGORY</t>
-  </si>
-  <si>
-    <t>study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">participant </t>
-  </si>
-  <si>
-    <t>NHATS_R12_Final_Release_SAS; NHATS_R12_SP_Sen_Dem_STATA</t>
-  </si>
-  <si>
-    <t>recode(3 = 1; 1:2= 0; -7:-9 = NA;  -1=NA; ELSE = NA)</t>
-  </si>
-  <si>
-    <t>recode(1:2= 1; 3:6 = 0; -7:-9 = NA; -1 = NA; ELSE = NA)</t>
-  </si>
-  <si>
-    <t>the study does not include an “other” category, therefore "No" category cannot be produced.</t>
-  </si>
-  <si>
-    <t>case_when(
-hc12cancerty2 %in% c(1,7) | 
-hc12cancerty3 %in% c(1,7) | 
-hc12cancerty4 %in% c(1,7) | 
-hc12cancerty5 %in% c(1,7) | 
-hc12cancerty6 %in% c(1,7) | 
-hc12cancerty7 %in% c(1,7) | 
-hc12cancerty8 %in% c(1,7) ~ 1;
-hc12cancerty2 == 2 &amp; 
-hc12cancerty3 == 2 &amp; 
-hc12cancerty4 == 2 &amp; 
-hc12cancerty5 == 2 &amp; 
-hc12cancerty6 == 2 &amp; 
-hc12cancerty7 == 2 &amp; 
-hc12cancerty8 == 2 ~ 0;
-TRUE ~ NA_integer_
-)</t>
-  </si>
-  <si>
-    <t>case_when(
-hc12trbfalbck %in% c(1,2,3) | hc12aslep30mn %in% c(1,2,3) ~ 1;
-hc12trbfalbck %in% c(4,7) &amp; hc12aslep30mn %in% c(4,5) ~ 0;
-TRUE ~ NA_integer_
-)</t>
-  </si>
-  <si>
-    <t>case_when(
-  hw12howtallft %in% c(-7, -8, -9, -1) |
-    hw12howtallin %in% c(-7, -8, -9, -1) |
-    hw12currweigh %in% c(-7, -8, -9, -1) ~ NA_real_,
-  !is.na(hw12howtallft) &amp; !is.na(hw12howtallin) &amp; !is.na(hw12currweigh) ~
-    (hw12currweigh * 0.453592) /
-    ((((hw12howtallft * 12) + hw12howtallin) * 0.0254)^2),
-  TRUE ~ NA_real_
-)</t>
-  </si>
-  <si>
-    <t>only the date of the activites booklet is completed and this is not necessairly the same date that the general questionnaire is completed. To confirm with the study</t>
-  </si>
-  <si>
-    <t>r12dmetnonmet</t>
-  </si>
-  <si>
-    <t>1= Metropolitan
-2= Non-metropolitan</t>
-  </si>
-  <si>
-    <t>Non metropolitan is not necessarily a rural area, therefore incompatible.</t>
-  </si>
-  <si>
-    <t>pa12vigoractv; pa12dfavact</t>
-  </si>
-  <si>
-    <t>R12 PA24 EVER VIGOROUS ACTIVITIES; R12 D FAVORITE ACTIVITY AT R12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">favourite activity considered as sports: 711 = Playing sports;
-715 = Exercise (gym, yoga, etc.) </t>
-  </si>
-  <si>
-    <t>case_when(
-  pa12vigoractv %in% c(-9, -8, -7, -1) |
-    pa12dfavact %in% c(-9, -8, -1, 997, 998, 999) ~ NA_real_,
-  pa12vigoractv == 1 |
-    pa12dfavact %in% c(711, 715) ~ 1,
-  pa12vigoractv == 2 &amp;
-    !pa12dfavact %in% c(711, 715) ~ 0,
-  TRUE ~ NA_integer_
-)</t>
-  </si>
-  <si>
-    <t>pa12dfavact</t>
-  </si>
-  <si>
-    <t>R12 D FAVORITE ACTIVITY AT R12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1 = Inapplicable
--8 = Don't know
--9 = Missing
-111 = Sleeping/Napping
-131 = Eating
-132 = Going out to eat
-199 = Other self-care activities
-211 = Work and work-related activities
-221 = Other income-generating activities
-241 = Volunteering
-299 = Other productive activities
-321 = Shopping for non-durable goods
-399 = Other shopping
-411 = Food and drink preparation
-434 = Outdoor maintenance
-439 = Household chores (indoor/outdoor unspecified)
-441 = Animal and pet care
-442 = Walking/exercising pets
-449 = Other animal and pet care
-451 = Vehicle maintenance and repair
-471 = Financial management
-499 = Other household activities
-511 = Physical care and assistance to others
-599 = Other physical care
-611 = Socializing in person
-612 = Socializing on the phone
-616 = Socializing/communicating on a computer
-621 = Watching TV/movies
-631 = Puzzles/games (not computer/online)
-632 = Gambling (not online/casino)
-636 = Puzzles/games (computer/online)
-641 = Arts, crafts, hobbies
-642 = Reading
-643 = Writing
-644 = Listening to music
-646 = Computer/online leisure
-651 = Smoking/tobacco use
-652 = Drinking alcohol
-661 = Doing nothing/relaxing
-669 = No activity
-699 = Other non-active leisure
-711 = Playing sports
-712 = Walking/jogging
-713 = Other outdoor recreation
-714 = Attending sporting events
-715 = Other physical activity (exercise, yoga, swimming, dancing)
-718 = Watching sporting events
-721 = Attending arts (plays, concerts)
-723 = Attending movies
-724 = Attending casinos
-737 = Leisure travel
-799 = Other active leisure
-811 = Attending religious activities
-812 = Other religious/spiritual activities
-821 = Attending meetings/events
-899 = Other organizational activity
-991 = Other miscellaneous
-992 = No favorite activity
-997 = Refused
-998 = Don't know
-999 = Not codeable
-</t>
-  </si>
-  <si>
-    <t>recode(
-  c(711, 712, 713, 715, 799, 737, 442, 434, 439, 451) = 1;
-  c(111, 131, 132, 199, 211, 221, 241, 299, 321, 399, 411, 441, 449, 471, 499, 511, 599, 611, 612, 616, 621, 631, 632, 636, 641, 642, 643, 644, 646, 651, 652, 661, 669, 699, 714, 718, 721, 723, 724, 811, 812, 821, 899, 991, 992) = 0;
-  c(-1, -8, -9, 997, 998, 999) = NA;
-  ELSE = NA
-)</t>
-  </si>
-  <si>
-    <t>favourite activity considered as physical activity:
-434 = Outdoor maintenance
-439 = Household chores (indoor/outdoor unspecified)
-442 = Walking/exercising pets
-451 = Vehicle maintenance and repair
-711 = Playing sports
-712 = Walking/jogging
-713 = Other outdoor recreation
-715 = Exercise (gym, yoga, swimming, dancing, etc.)
-737 = Leisure travel
-799 = Other active leisure</t>
-  </si>
-  <si>
-    <t>recode(c(1,7) = 1; 2 = 0; c(-9,-8,-7) = NA; -1 = NA; ELSE = NA)</t>
-  </si>
-  <si>
-    <t>recode(5 = 1; 4 = 2; 3 = 3; c(1,2) = 4; ELSE = NA)</t>
-  </si>
-  <si>
-    <t>r12dgender</t>
-  </si>
-  <si>
-    <t>R12 D GENDER OF SP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recode(5=1; 4 = 2; 3= 3; 1:2=4; ELSE=NA) </t>
-  </si>
-  <si>
-    <t>-9 = Missing; 
--7 = RF;
--8 = DK;
--1 = Inapplicable;
-1 = YES;
-2 = NO
-7 = PREVIOUSLY REPORTED</t>
-  </si>
-  <si>
-    <t>case_when(
-dt12getoplcs1 == 1 | ha12howgtstr7 == 1 ~ 1;
-dt12getoplcs1 == 2 &amp; ha12howgtstr7 == 2 ~ 0;
-TRUE ~ NA_integer_
-)</t>
-  </si>
-  <si>
-    <t>r12dintvwrage</t>
   </si>
 </sst>
 </file>
@@ -1757,7 +1602,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1796,6 +1641,14 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2138,41 +1991,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABC73F24-28B6-451D-9DE2-0CD6B57BA63C}">
   <dimension ref="A1:Y164"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.1328125" customWidth="1"/>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="37.1328125" customWidth="1"/>
-    <col min="5" max="5" width="22.3984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.73046875" customWidth="1"/>
-    <col min="8" max="8" width="25.265625" customWidth="1"/>
-    <col min="9" max="9" width="27.86328125" customWidth="1"/>
+    <col min="4" max="4" width="37.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" customWidth="1"/>
+    <col min="9" max="9" width="27.85546875" customWidth="1"/>
     <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="57.3984375" style="2" customWidth="1"/>
-    <col min="12" max="13" width="70.3984375" style="3" customWidth="1"/>
-    <col min="14" max="16" width="22.1328125" customWidth="1"/>
-    <col min="17" max="17" width="24.59765625" customWidth="1"/>
-    <col min="18" max="19" width="31.86328125" customWidth="1"/>
-    <col min="20" max="20" width="21.1328125" customWidth="1"/>
-    <col min="21" max="21" width="28.3984375" customWidth="1"/>
-    <col min="22" max="22" width="23.73046875" customWidth="1"/>
-    <col min="23" max="23" width="27.73046875" customWidth="1"/>
-    <col min="24" max="24" width="61.59765625" customWidth="1"/>
-    <col min="25" max="25" width="31.33203125" customWidth="1"/>
+    <col min="11" max="11" width="57.42578125" style="2" customWidth="1"/>
+    <col min="12" max="13" width="70.42578125" style="3" customWidth="1"/>
+    <col min="14" max="16" width="22.140625" customWidth="1"/>
+    <col min="17" max="17" width="24.5703125" customWidth="1"/>
+    <col min="18" max="19" width="31.85546875" customWidth="1"/>
+    <col min="20" max="20" width="21.140625" customWidth="1"/>
+    <col min="21" max="21" width="28.42578125" customWidth="1"/>
+    <col min="22" max="22" width="23.7109375" customWidth="1"/>
+    <col min="23" max="23" width="27.7109375" customWidth="1"/>
+    <col min="24" max="24" width="61.5703125" customWidth="1"/>
+    <col min="25" max="25" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>365</v>
+        <v>319</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>3</v>
@@ -2181,10 +2034,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>366</v>
+        <v>320</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>367</v>
+        <v>321</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>1</v>
@@ -2193,37 +2046,37 @@
         <v>5</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>368</v>
+        <v>322</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="N1" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="O1" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="Q1" s="13" t="s">
-        <v>280</v>
-      </c>
       <c r="R1" s="10" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="S1" s="14" t="s">
         <v>9</v>
       </c>
       <c r="T1" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="U1" s="15" t="s">
         <v>281</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>282</v>
       </c>
       <c r="V1" s="15" t="s">
         <v>6</v>
@@ -2235,15 +2088,15 @@
         <v>8</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -2258,27 +2111,27 @@
         <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" t="s">
         <v>284</v>
-      </c>
-      <c r="K2" t="s">
-        <v>285</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M2"/>
       <c r="N2" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O2" s="16"/>
       <c r="P2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="R2" s="16"/>
       <c r="S2" s="4"/>
@@ -2289,45 +2142,45 @@
         <v>27</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>371</v>
+        <v>325</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K3"/>
       <c r="N3" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O3" s="16"/>
       <c r="Q3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
@@ -2338,19 +2191,19 @@
         <v>27</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="X3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -2369,18 +2222,18 @@
       </c>
       <c r="H4" s="2"/>
       <c r="I4" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O4" s="16"/>
       <c r="R4" s="4"/>
@@ -2389,7 +2242,7 @@
         <v>14</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>14</v>
@@ -2398,15 +2251,15 @@
         <v>14</v>
       </c>
       <c r="Y4" s="11" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
@@ -2424,47 +2277,47 @@
         <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="K5" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U5" t="s">
         <v>26</v>
       </c>
       <c r="V5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="W5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C6" t="s">
         <v>29</v>
@@ -2483,27 +2336,25 @@
       </c>
       <c r="H6" s="2"/>
       <c r="I6" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>404</v>
+        <v>330</v>
       </c>
       <c r="K6" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="5" t="s">
-        <v>16</v>
-      </c>
+      <c r="M6" s="5"/>
       <c r="N6" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O6" s="16"/>
       <c r="P6" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R6" t="s">
         <v>32</v>
@@ -2521,12 +2372,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:25" ht="120" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
@@ -2544,15 +2395,15 @@
         <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O7" s="16"/>
       <c r="S7" s="2"/>
@@ -2569,15 +2420,15 @@
         <v>14</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C8" t="s">
         <v>39</v>
@@ -2595,27 +2446,27 @@
         <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J8" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="K8" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O8" s="16"/>
       <c r="P8" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U8" t="s">
         <v>26</v>
@@ -2627,15 +2478,15 @@
         <v>38</v>
       </c>
       <c r="X8" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C9" t="s">
         <v>43</v>
@@ -2653,27 +2504,27 @@
         <v>46</v>
       </c>
       <c r="I9" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J9" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="K9" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O9" s="16"/>
       <c r="P9" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U9" s="4" t="s">
         <v>26</v>
@@ -2685,15 +2536,15 @@
         <v>51</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
@@ -2708,26 +2559,26 @@
         <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J10" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="K10" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="N10" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O10" s="16"/>
       <c r="P10" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="U10" t="s">
         <v>26</v>
@@ -2742,12 +2593,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
@@ -2762,26 +2613,26 @@
         <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J11" t="s">
-        <v>373</v>
+        <v>338</v>
       </c>
       <c r="K11" t="s">
-        <v>374</v>
+        <v>339</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="N11" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O11" s="16"/>
       <c r="P11" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U11" t="s">
         <v>26</v>
@@ -2796,12 +2647,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C12" t="s">
         <v>55</v>
@@ -2819,27 +2670,27 @@
         <v>58</v>
       </c>
       <c r="I12" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J12" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="K12" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="L12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M12"/>
       <c r="N12" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O12" s="16"/>
       <c r="P12" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U12" t="s">
         <v>26</v>
@@ -2851,15 +2702,15 @@
         <v>38</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="171" x14ac:dyDescent="0.45">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="180" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C13" t="s">
         <v>59</v>
@@ -2877,10 +2728,10 @@
         <v>62</v>
       </c>
       <c r="I13" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J13" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="K13" t="s">
         <v>341</v>
@@ -2890,14 +2741,14 @@
       </c>
       <c r="M13" s="5"/>
       <c r="N13" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O13" s="16"/>
       <c r="U13" t="s">
         <v>14</v>
       </c>
       <c r="V13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="W13" t="s">
         <v>14</v>
@@ -2905,16 +2756,16 @@
       <c r="X13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Y13" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="171" x14ac:dyDescent="0.45">
+      <c r="Y13" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="180" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C14" t="s">
         <v>63</v>
@@ -2932,10 +2783,10 @@
         <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J14" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="K14" t="s">
         <v>341</v>
@@ -2945,14 +2796,14 @@
       </c>
       <c r="M14" s="5"/>
       <c r="N14" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O14" s="16"/>
       <c r="P14" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U14" t="s">
         <v>26</v>
@@ -2964,15 +2815,15 @@
         <v>38</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="195" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C15" t="s">
         <v>67</v>
@@ -2990,49 +2841,47 @@
         <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>377</v>
-      </c>
-      <c r="J15" t="s">
-        <v>385</v>
+        <v>388</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>342</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>386</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="L15" s="17"/>
       <c r="N15" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O15" s="16"/>
       <c r="P15" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>14</v>
+        <v>389</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>289</v>
+        <v>389</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>14</v>
+        <v>389</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
+        <v>389</v>
+      </c>
+      <c r="Y15" s="19" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="135" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C16" t="s">
         <v>70</v>
@@ -3051,29 +2900,29 @@
       </c>
       <c r="H16" s="2"/>
       <c r="I16" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N16" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O16" s="16"/>
       <c r="P16" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q16" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="U16" t="s">
         <v>26</v>
@@ -3085,15 +2934,15 @@
         <v>75</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C17" t="s">
         <v>76</v>
@@ -3111,20 +2960,20 @@
         <v>78</v>
       </c>
       <c r="I17" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N17" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O17" s="16"/>
       <c r="P17" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U17" s="4" t="s">
         <v>26</v>
@@ -3133,18 +2982,18 @@
         <v>27</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="X17" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C18" t="s">
         <v>79</v>
@@ -3163,23 +3012,23 @@
       </c>
       <c r="H18" s="2"/>
       <c r="I18" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J18" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="K18" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="N18" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O18" s="16"/>
       <c r="P18" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q18" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R18" t="s">
         <v>82</v>
@@ -3194,15 +3043,15 @@
         <v>75</v>
       </c>
       <c r="X18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C19" t="s">
         <v>83</v>
@@ -3220,20 +3069,20 @@
         <v>78</v>
       </c>
       <c r="I19" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N19" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O19" s="16"/>
       <c r="P19" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q19" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U19" s="4" t="s">
         <v>26</v>
@@ -3242,18 +3091,18 @@
         <v>27</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="X19" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="156.75" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:24" ht="210" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C20" t="s">
         <v>85</v>
@@ -3271,26 +3120,26 @@
         <v>87</v>
       </c>
       <c r="I20" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="N20" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O20" s="16"/>
       <c r="P20" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U20" t="s">
         <v>26</v>
@@ -3299,18 +3148,18 @@
         <v>37</v>
       </c>
       <c r="W20" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" t="s">
         <v>88</v>
@@ -3329,23 +3178,23 @@
       </c>
       <c r="H21" s="2"/>
       <c r="I21" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J21" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="K21" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="N21" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O21" s="16"/>
       <c r="P21" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q21" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R21" t="s">
         <v>74</v>
@@ -3360,15 +3209,15 @@
         <v>75</v>
       </c>
       <c r="X21" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" ht="57" x14ac:dyDescent="0.45">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="60" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" t="s">
         <v>90</v>
@@ -3386,27 +3235,27 @@
         <v>78</v>
       </c>
       <c r="I22" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J22" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="K22" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O22" s="16"/>
       <c r="P22" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q22" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U22" t="s">
         <v>26</v>
@@ -3418,15 +3267,15 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C23" t="s">
         <v>92</v>
@@ -3444,25 +3293,25 @@
         <v>94</v>
       </c>
       <c r="I23" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J23" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N23" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O23" s="16"/>
       <c r="P23" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C24" t="s">
         <v>95</v>
@@ -3477,13 +3326,13 @@
         <v>13</v>
       </c>
       <c r="I24" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N24" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O24" s="16"/>
       <c r="U24" s="4" t="s">
@@ -3499,12 +3348,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C25" t="s">
         <v>97</v>
@@ -3522,13 +3371,13 @@
         <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J25" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N25" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O25" s="16"/>
       <c r="U25" s="4" t="s">
@@ -3544,12 +3393,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C26" t="s">
         <v>101</v>
@@ -3567,13 +3416,13 @@
         <v>100</v>
       </c>
       <c r="I26" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J26" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O26" s="16"/>
       <c r="U26" s="4" t="s">
@@ -3589,12 +3438,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C27" t="s">
         <v>104</v>
@@ -3612,13 +3461,13 @@
         <v>106</v>
       </c>
       <c r="I27" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N27" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O27" s="16"/>
       <c r="U27" s="4" t="s">
@@ -3634,12 +3483,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C28" t="s">
         <v>107</v>
@@ -3658,13 +3507,13 @@
       </c>
       <c r="H28" s="2"/>
       <c r="I28" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N28" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O28" s="16"/>
       <c r="U28" s="4" t="s">
@@ -3680,12 +3529,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C29" t="s">
         <v>110</v>
@@ -3703,13 +3552,13 @@
         <v>112</v>
       </c>
       <c r="I29" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N29" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O29" s="16"/>
       <c r="U29" s="4" t="s">
@@ -3725,12 +3574,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C30" t="s">
         <v>113</v>
@@ -3748,13 +3597,13 @@
         <v>115</v>
       </c>
       <c r="I30" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N30" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O30" s="16"/>
       <c r="U30" s="4" t="s">
@@ -3770,12 +3619,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C31" t="s">
         <v>116</v>
@@ -3793,13 +3642,13 @@
         <v>118</v>
       </c>
       <c r="I31" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N31" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O31" s="16"/>
       <c r="U31" s="4" t="s">
@@ -3815,12 +3664,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C32" t="s">
         <v>119</v>
@@ -3838,13 +3687,13 @@
         <v>121</v>
       </c>
       <c r="I32" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N32" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O32" s="16"/>
       <c r="U32" s="4" t="s">
@@ -3860,12 +3709,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C33" t="s">
         <v>122</v>
@@ -3883,13 +3732,13 @@
         <v>121</v>
       </c>
       <c r="I33" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J33" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N33" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O33" s="16"/>
       <c r="U33" s="4" t="s">
@@ -3905,12 +3754,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C34" t="s">
         <v>124</v>
@@ -3928,13 +3777,13 @@
         <v>121</v>
       </c>
       <c r="I34" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J34" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N34" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O34" s="16"/>
       <c r="U34" s="4" t="s">
@@ -3950,12 +3799,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C35" t="s">
         <v>126</v>
@@ -3973,13 +3822,13 @@
         <v>121</v>
       </c>
       <c r="I35" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N35" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O35" s="16"/>
       <c r="U35" s="4" t="s">
@@ -3995,12 +3844,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C36" t="s">
         <v>128</v>
@@ -4018,13 +3867,13 @@
         <v>121</v>
       </c>
       <c r="I36" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N36" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O36" s="16"/>
       <c r="U36" s="4" t="s">
@@ -4040,12 +3889,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C37" t="s">
         <v>130</v>
@@ -4063,13 +3912,13 @@
         <v>132</v>
       </c>
       <c r="I37" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J37" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N37" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O37" s="16"/>
       <c r="U37" s="4" t="s">
@@ -4085,12 +3934,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C38" t="s">
         <v>133</v>
@@ -4109,13 +3958,13 @@
       </c>
       <c r="H38" s="2"/>
       <c r="I38" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J38" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N38" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O38" s="16"/>
       <c r="U38" s="4" t="s">
@@ -4131,12 +3980,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:25" s="2" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:25" s="2" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>137</v>
@@ -4154,15 +4003,15 @@
         <v>140</v>
       </c>
       <c r="I39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O39" s="16"/>
       <c r="P39"/>
@@ -4182,12 +4031,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C40" t="s">
         <v>141</v>
@@ -4206,13 +4055,13 @@
       </c>
       <c r="H40" s="2"/>
       <c r="I40" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J40" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N40" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O40" s="16"/>
       <c r="U40" s="4" t="s">
@@ -4228,12 +4077,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C41" t="s">
         <v>144</v>
@@ -4251,13 +4100,13 @@
         <v>140</v>
       </c>
       <c r="I41" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N41" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O41" s="16"/>
       <c r="U41" s="4" t="s">
@@ -4273,12 +4122,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C42" t="s">
         <v>147</v>
@@ -4296,13 +4145,13 @@
         <v>149</v>
       </c>
       <c r="I42" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J42" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N42" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O42" s="16"/>
       <c r="U42" s="4" t="s">
@@ -4318,12 +4167,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C43" t="s">
         <v>150</v>
@@ -4342,13 +4191,13 @@
       </c>
       <c r="H43" s="2"/>
       <c r="I43" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J43" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N43" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O43" s="16"/>
       <c r="U43" s="4" t="s">
@@ -4364,12 +4213,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="57" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C44" t="s">
         <v>154</v>
@@ -4387,13 +4236,13 @@
         <v>156</v>
       </c>
       <c r="I44" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N44" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O44" s="16"/>
       <c r="U44" s="4" t="s">
@@ -4409,12 +4258,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C45" t="s">
         <v>157</v>
@@ -4432,20 +4281,20 @@
         <v>160</v>
       </c>
       <c r="I45" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J45" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="K45" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M45" s="5"/>
       <c r="N45" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O45" s="16"/>
       <c r="S45" s="2"/>
@@ -4453,24 +4302,24 @@
         <v>14</v>
       </c>
       <c r="V45" t="s">
+        <v>305</v>
+      </c>
+      <c r="W45" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="X45" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y45" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="W45" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="X45" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y45" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="46" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C46" t="s">
         <v>161</v>
@@ -4488,27 +4337,27 @@
         <v>163</v>
       </c>
       <c r="I46" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J46" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="K46" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="L46" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="L46" s="5" t="s">
-        <v>165</v>
       </c>
       <c r="M46" s="5"/>
       <c r="N46" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O46" s="16"/>
       <c r="U46" t="s">
         <v>14</v>
       </c>
       <c r="V46" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>14</v>
@@ -4517,51 +4366,51 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C47" t="s">
+        <v>165</v>
+      </c>
+      <c r="D47" t="s">
         <v>166</v>
       </c>
-      <c r="D47" t="s">
-        <v>167</v>
-      </c>
       <c r="E47" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F47" t="s">
         <v>50</v>
       </c>
       <c r="G47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J47" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="K47" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M47" s="5"/>
       <c r="N47" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O47" s="16"/>
       <c r="P47" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q47" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U47" t="s">
         <v>26</v>
@@ -4573,53 +4422,53 @@
         <v>51</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" ht="135" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C48" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48" t="s">
         <v>169</v>
       </c>
-      <c r="D48" t="s">
-        <v>170</v>
-      </c>
       <c r="E48" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I48" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J48" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="K48" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M48" s="5"/>
       <c r="N48" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O48" s="16"/>
       <c r="P48" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q48" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U48" t="s">
         <v>26</v>
@@ -4631,56 +4480,53 @@
         <v>38</v>
       </c>
       <c r="X48" t="s">
-        <v>398</v>
-      </c>
-      <c r="Y48" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" ht="213.75" x14ac:dyDescent="0.45">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" ht="225" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C49" t="s">
+        <v>171</v>
+      </c>
+      <c r="D49" t="s">
         <v>172</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I49" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J49" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M49" s="5"/>
       <c r="N49" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O49" s="16"/>
       <c r="P49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q49" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S49" s="2"/>
       <c r="U49" t="s">
@@ -4693,56 +4539,56 @@
         <v>51</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" ht="213.75" x14ac:dyDescent="0.45">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" ht="225" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C50" t="s">
+        <v>175</v>
+      </c>
+      <c r="D50" t="s">
         <v>176</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I50" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J50" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M50" s="5"/>
       <c r="N50" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O50" s="16"/>
       <c r="P50" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q50" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S50" s="2"/>
       <c r="U50" t="s">
@@ -4755,56 +4601,56 @@
         <v>51</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C51" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" t="s">
         <v>179</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I51" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J51" t="s">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="K51" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="L51" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M51" s="5"/>
       <c r="N51" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O51" s="16"/>
       <c r="P51" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q51" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U51" t="s">
         <v>26</v>
@@ -4816,41 +4662,41 @@
         <v>51</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" ht="120" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C52" t="s">
+        <v>182</v>
+      </c>
+      <c r="D52" t="s">
         <v>183</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I52" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J52" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O52" s="16"/>
       <c r="U52" s="4" t="s">
@@ -4866,50 +4712,50 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="270.75" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:25" ht="285" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C53" t="s">
+        <v>186</v>
+      </c>
+      <c r="D53" t="s">
         <v>187</v>
       </c>
-      <c r="D53" t="s">
-        <v>188</v>
-      </c>
       <c r="E53" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I53" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="L53" s="5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M53" s="5"/>
       <c r="N53" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O53" s="16"/>
       <c r="P53" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q53" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U53" t="s">
         <v>26</v>
@@ -4921,39 +4767,42 @@
         <v>51</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+        <v>386</v>
+      </c>
+      <c r="Y53" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C54" t="s">
+        <v>188</v>
+      </c>
+      <c r="D54" t="s">
         <v>189</v>
       </c>
-      <c r="D54" t="s">
-        <v>190</v>
-      </c>
       <c r="E54" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I54" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J54" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N54" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O54" s="16"/>
       <c r="U54" s="4" t="s">
@@ -4969,38 +4818,38 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C55" t="s">
+        <v>190</v>
+      </c>
+      <c r="D55" t="s">
         <v>191</v>
       </c>
-      <c r="D55" t="s">
-        <v>192</v>
-      </c>
       <c r="E55" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I55" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J55" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O55" s="16"/>
       <c r="U55" s="4" t="s">
@@ -5016,38 +4865,38 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C56" t="s">
+        <v>192</v>
+      </c>
+      <c r="D56" t="s">
         <v>193</v>
       </c>
-      <c r="D56" t="s">
-        <v>194</v>
-      </c>
       <c r="E56" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I56" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J56" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O56" s="16"/>
       <c r="U56" s="4" t="s">
@@ -5063,36 +4912,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C57" t="s">
+        <v>194</v>
+      </c>
+      <c r="D57" t="s">
         <v>195</v>
       </c>
-      <c r="D57" t="s">
-        <v>196</v>
-      </c>
       <c r="E57" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I57" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J57" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N57" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O57" s="16"/>
       <c r="U57" s="4" t="s">
@@ -5108,36 +4957,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="57" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C58" t="s">
+        <v>196</v>
+      </c>
+      <c r="D58" t="s">
         <v>197</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I58" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J58" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N58" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O58" s="16"/>
       <c r="U58" s="4" t="s">
@@ -5153,33 +5002,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C59" t="s">
+        <v>199</v>
+      </c>
+      <c r="D59" t="s">
         <v>200</v>
       </c>
-      <c r="D59" t="s">
-        <v>201</v>
-      </c>
       <c r="E59" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
       </c>
       <c r="I59" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J59" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N59" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O59" s="16"/>
       <c r="U59" s="4" t="s">
@@ -5195,33 +5044,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C60" t="s">
+        <v>201</v>
+      </c>
+      <c r="D60" t="s">
         <v>202</v>
       </c>
-      <c r="D60" t="s">
-        <v>203</v>
-      </c>
       <c r="E60" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
       </c>
       <c r="I60" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J60" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N60" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O60" s="16"/>
       <c r="U60" s="4" t="s">
@@ -5237,33 +5086,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C61" t="s">
+        <v>203</v>
+      </c>
+      <c r="D61" t="s">
         <v>204</v>
       </c>
-      <c r="D61" t="s">
-        <v>205</v>
-      </c>
       <c r="E61" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
       </c>
       <c r="I61" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J61" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N61" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O61" s="16"/>
       <c r="U61" s="4" t="s">
@@ -5279,33 +5128,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C62" t="s">
+        <v>205</v>
+      </c>
+      <c r="D62" t="s">
         <v>206</v>
       </c>
-      <c r="D62" t="s">
-        <v>207</v>
-      </c>
       <c r="E62" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
       </c>
       <c r="I62" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J62" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N62" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O62" s="16"/>
       <c r="U62" s="4" t="s">
@@ -5321,33 +5170,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C63" t="s">
+        <v>207</v>
+      </c>
+      <c r="D63" t="s">
         <v>208</v>
       </c>
-      <c r="D63" t="s">
-        <v>209</v>
-      </c>
       <c r="E63" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F63" t="s">
         <v>16</v>
       </c>
       <c r="I63" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J63" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N63" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O63" s="16"/>
       <c r="S63" s="2"/>
@@ -5365,33 +5214,33 @@
       </c>
       <c r="Y63" s="2"/>
     </row>
-    <row r="64" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C64" t="s">
+        <v>209</v>
+      </c>
+      <c r="D64" t="s">
         <v>210</v>
       </c>
-      <c r="D64" t="s">
-        <v>211</v>
-      </c>
       <c r="E64" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
       </c>
       <c r="I64" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N64" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O64" s="16"/>
       <c r="U64" s="4" t="s">
@@ -5407,34 +5256,34 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C65" t="s">
+        <v>211</v>
+      </c>
+      <c r="D65" t="s">
         <v>212</v>
       </c>
-      <c r="D65" t="s">
-        <v>213</v>
-      </c>
       <c r="E65" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N65" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O65" s="16"/>
       <c r="U65" s="4" t="s">
@@ -5450,50 +5299,50 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C66" t="s">
+        <v>213</v>
+      </c>
+      <c r="D66" t="s">
         <v>214</v>
       </c>
-      <c r="D66" t="s">
-        <v>215</v>
-      </c>
       <c r="E66" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F66" t="s">
         <v>16</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I66" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J66" t="s">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="K66" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>402</v>
+        <v>310</v>
       </c>
       <c r="M66" s="5"/>
       <c r="N66" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O66" s="16"/>
       <c r="P66" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q66" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S66" s="2"/>
       <c r="U66" t="s">
@@ -5506,41 +5355,41 @@
         <v>38</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>397</v>
+        <v>311</v>
       </c>
       <c r="Y66" s="2"/>
     </row>
-    <row r="67" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C67" t="s">
+        <v>216</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="E67" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F67" t="s">
         <v>50</v>
       </c>
       <c r="G67" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J67" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N67" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O67" s="16"/>
       <c r="U67" s="4" t="s">
@@ -5556,36 +5405,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:25" ht="135" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C68" t="s">
+        <v>219</v>
+      </c>
+      <c r="D68" t="s">
         <v>220</v>
       </c>
-      <c r="D68" t="s">
-        <v>221</v>
-      </c>
       <c r="E68" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I68" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J68" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N68" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O68" s="16"/>
       <c r="U68" s="4" t="s">
@@ -5601,50 +5450,50 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="142.5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:25" ht="150" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C69" t="s">
+        <v>222</v>
+      </c>
+      <c r="D69" t="s">
         <v>223</v>
       </c>
-      <c r="D69" t="s">
-        <v>224</v>
-      </c>
       <c r="E69" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F69" t="s">
         <v>16</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I69" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J69" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="L69" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="M69" s="5"/>
       <c r="N69" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O69" s="16"/>
       <c r="P69" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q69" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U69" t="s">
         <v>26</v>
@@ -5656,39 +5505,39 @@
         <v>51</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C70" t="s">
+        <v>225</v>
+      </c>
+      <c r="D70" t="s">
         <v>226</v>
       </c>
-      <c r="D70" t="s">
-        <v>227</v>
-      </c>
       <c r="E70" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F70" t="s">
         <v>16</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I70" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J70" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N70" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O70" s="16"/>
       <c r="U70" s="4" t="s">
@@ -5704,36 +5553,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C71" t="s">
+        <v>228</v>
+      </c>
+      <c r="D71" t="s">
         <v>229</v>
       </c>
-      <c r="D71" t="s">
-        <v>230</v>
-      </c>
       <c r="E71" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I71" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J71" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N71" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O71" s="16"/>
       <c r="U71" s="4" t="s">
@@ -5749,34 +5598,34 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C72" t="s">
+        <v>230</v>
+      </c>
+      <c r="D72" t="s">
         <v>231</v>
       </c>
-      <c r="D72" t="s">
-        <v>232</v>
-      </c>
       <c r="E72" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F72" t="s">
         <v>16</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J72" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N72" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O72" s="16"/>
       <c r="U72" s="4" t="s">
@@ -5792,36 +5641,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="216" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:25" ht="216" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C73" t="s">
+        <v>232</v>
+      </c>
+      <c r="D73" t="s">
         <v>233</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="F73" t="s">
         <v>16</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I73" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J73" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N73" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O73" s="16"/>
       <c r="U73" s="4" t="s">
@@ -5837,36 +5686,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C74" t="s">
+        <v>236</v>
+      </c>
+      <c r="D74" t="s">
         <v>237</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I74" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N74" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O74" s="16"/>
       <c r="U74" s="4" t="s">
@@ -5882,36 +5731,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="57" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C75" t="s">
+        <v>240</v>
+      </c>
+      <c r="D75" t="s">
         <v>241</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="F75" t="s">
         <v>16</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I75" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J75" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N75" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O75" s="16"/>
       <c r="U75" s="4" t="s">
@@ -5927,37 +5776,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C76" t="s">
+        <v>244</v>
+      </c>
+      <c r="D76" t="s">
         <v>245</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="F76" t="s">
         <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J76" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N76" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O76" s="16"/>
       <c r="S76" s="2"/>
@@ -5975,36 +5824,36 @@
       </c>
       <c r="Y76" s="2"/>
     </row>
-    <row r="77" spans="1:25" ht="142.5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:25" ht="165" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C77" t="s">
+        <v>247</v>
+      </c>
+      <c r="D77" t="s">
         <v>248</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="F77" t="s">
         <v>16</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I77" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J77" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N77" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O77" s="16"/>
       <c r="U77" s="4" t="s">
@@ -6020,36 +5869,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C78" t="s">
+        <v>251</v>
+      </c>
+      <c r="D78" t="s">
         <v>252</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I78" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J78" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N78" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O78" s="16"/>
       <c r="U78" s="4" t="s">
@@ -6065,36 +5914,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:25" ht="120" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C79" t="s">
+        <v>255</v>
+      </c>
+      <c r="D79" t="s">
         <v>256</v>
       </c>
-      <c r="D79" t="s">
-        <v>257</v>
-      </c>
       <c r="E79" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F79" t="s">
         <v>16</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I79" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J79" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N79" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O79" s="16"/>
       <c r="U79" s="4" t="s">
@@ -6110,50 +5959,50 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="409.5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:25" ht="165" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C80" t="s">
+        <v>258</v>
+      </c>
+      <c r="D80" t="s">
         <v>259</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="F80" t="s">
         <v>16</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I80" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J80" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="K80" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>310</v>
+        <v>398</v>
       </c>
       <c r="M80" s="5"/>
       <c r="N80" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O80" s="16"/>
       <c r="P80" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q80" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S80" s="2"/>
       <c r="U80" t="s">
@@ -6163,59 +6012,57 @@
         <v>37</v>
       </c>
       <c r="W80" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="Y80" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="81" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
+        <v>399</v>
+      </c>
+      <c r="Y80" s="2"/>
+    </row>
+    <row r="81" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C81" t="s">
+        <v>261</v>
+      </c>
+      <c r="D81" t="s">
         <v>262</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="F81" t="s">
         <v>16</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I81" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J81" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="K81" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="L81" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="M81" s="5"/>
       <c r="N81" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O81" s="16"/>
       <c r="P81" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q81" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U81" t="s">
         <v>26</v>
@@ -6227,98 +6074,98 @@
         <v>51</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="82" spans="1:25" ht="409.5" x14ac:dyDescent="0.45">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C82" t="s">
+        <v>264</v>
+      </c>
+      <c r="D82" t="s">
         <v>265</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F82" t="s">
         <v>16</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I82" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="K82" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="L82" s="5" t="s">
+      <c r="K82" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="M82" s="5"/>
+      <c r="L82" s="20"/>
+      <c r="M82" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="N82" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O82" s="16"/>
       <c r="P82" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q82" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S82" s="2"/>
       <c r="U82" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="V82" t="s">
-        <v>37</v>
+        <v>305</v>
       </c>
       <c r="W82" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="X82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y82" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="Y82" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="83" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="83" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C83" t="s">
+        <v>267</v>
+      </c>
+      <c r="D83" t="s">
         <v>268</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="F83" t="s">
         <v>50</v>
       </c>
       <c r="I83" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N83" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O83" s="16"/>
       <c r="U83" s="4" t="s">
@@ -6334,38 +6181,38 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C84" t="s">
+        <v>270</v>
+      </c>
+      <c r="D84" t="s">
         <v>271</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="F84" t="s">
         <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I84" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
       <c r="N84" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="O84" s="16"/>
       <c r="U84" s="4" t="s">
@@ -6381,172 +6228,172 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="L88" s="8"/>
       <c r="M88" s="8"/>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="L96" s="5"/>
       <c r="M96" s="5"/>
     </row>
-    <row r="97" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="97" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
     </row>
-    <row r="99" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="99" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="W99" s="9"/>
       <c r="X99" s="9"/>
     </row>
-    <row r="101" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="101" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
     </row>
-    <row r="102" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="102" spans="8:24" x14ac:dyDescent="0.25">
       <c r="J102" s="2"/>
     </row>
-    <row r="103" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="103" spans="8:24" x14ac:dyDescent="0.25">
       <c r="J103" s="2"/>
     </row>
-    <row r="104" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="104" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
     </row>
-    <row r="111" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="111" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
     </row>
-    <row r="121" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="121" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
     </row>
-    <row r="123" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="123" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
     </row>
-    <row r="126" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="126" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
     </row>
-    <row r="127" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="127" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
     </row>
-    <row r="128" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="128" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
     </row>
-    <row r="130" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="130" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
       <c r="L130" s="5"/>
       <c r="M130" s="5"/>
     </row>
-    <row r="131" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="131" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
     </row>
-    <row r="132" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="132" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
     </row>
-    <row r="133" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="133" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
     </row>
-    <row r="134" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="134" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
     </row>
-    <row r="135" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="135" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
     </row>
-    <row r="136" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="136" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
     </row>
-    <row r="137" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="137" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
     </row>
-    <row r="138" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="138" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
     </row>
-    <row r="139" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="139" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
     </row>
-    <row r="140" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="140" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
       <c r="L140" s="8"/>
       <c r="M140" s="8"/>
     </row>
-    <row r="148" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="148" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
       <c r="L148" s="8"/>
       <c r="M148" s="8"/>
     </row>
-    <row r="150" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="150" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
     </row>
-    <row r="151" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="151" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
     </row>
-    <row r="152" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="152" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
     </row>
-    <row r="153" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="153" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
     </row>
-    <row r="154" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="154" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
     </row>
-    <row r="155" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="155" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
     </row>
-    <row r="156" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="156" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
     </row>
-    <row r="157" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="157" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
     </row>
-    <row r="159" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="159" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
       <c r="L159" s="5"/>
@@ -6554,25 +6401,25 @@
       <c r="W159" s="9"/>
       <c r="X159" s="9"/>
     </row>
-    <row r="160" spans="8:24" x14ac:dyDescent="0.45">
+    <row r="160" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
       <c r="L160" s="5"/>
       <c r="M160" s="5"/>
     </row>
-    <row r="161" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="161" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
     </row>
-    <row r="162" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="162" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
     </row>
-    <row r="163" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="163" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
     </row>
-    <row r="164" spans="8:13" x14ac:dyDescent="0.45">
+    <row r="164" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
       <c r="L164" s="5"/>

--- a/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17bc974f5891b333/Documents/ProPASS/Harmo/NHATS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="8_{B04BC2F6-0886-423B-9CF8-2AF8452D03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEE8A9EB-BF23-4F9D-9D09-C606FCA899DC}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="8_{B04BC2F6-0886-423B-9CF8-2AF8452D03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32DD84DE-0198-46E0-8A8F-FA88CCBB9112}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F744FAC3-0BAB-4C7A-92B3-0824573F48DB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F744FAC3-0BAB-4C7A-92B3-0824573F48DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="401">
   <si>
     <t>index</t>
   </si>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>Completion date</t>
-  </si>
-  <si>
-    <t>Date on which the questionnaire was completed</t>
   </si>
   <si>
     <t>date</t>
@@ -1001,9 +998,6 @@
     <t>hrs/week</t>
   </si>
   <si>
-    <t>recode (3 = 1; c(1,2) = 0; c(-9,-8,-7,-1) = NA; ELSE = NA)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 = Married; 
 2 = Living with a partner;
 3 = Separated;
@@ -1017,9 +1011,6 @@
 </t>
   </si>
   <si>
-    <t>recode (c(1,2) = 1; c(3,4,5,6) = 0; c(-9,-8,-7) = NA; -1 = NA; ELSE = NA)</t>
-  </si>
-  <si>
     <t>“Living with a partner” does not imply ever married. Since this category cannot be classified with certainty into the DataSchema categories, the variable is considered incompatible.</t>
   </si>
   <si>
@@ -1068,9 +1059,6 @@
 3 = Good;
 4 = Fair;
 5 = Poor</t>
-  </si>
-  <si>
-    <t>recode (5 = 1; 4 = 2; 3 = 3; c(1,2) = 4; ELSE = NA)</t>
   </si>
   <si>
     <t xml:space="preserve">-7 = DF;
@@ -1101,9 +1089,6 @@
 7 = PREVIOUSLY REPORTED</t>
   </si>
   <si>
-    <t>recode (c(1,7) = 1; 2 = 0; c(-9,-8,-7) = NA; -1 = NA; ELSE = NA)</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 -7 = RF
 -9 = Missing;
@@ -1125,13 +1110,6 @@
 </t>
   </si>
   <si>
-    <t>case_when(
-dt11getoplcs1 == 1 | ha11howgtstr7 == 1 ~ 1;
-dt11getoplcs1 == 2 &amp; ha11howgtstr7 == 2 ~ 0;
-TRUE ~ NA_integer
-)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Questionnaire </t>
   </si>
   <si>
@@ -1166,9 +1144,6 @@
   </si>
   <si>
     <t>only the date of the activites booklet is completed and this is not necessairly the same date that the general questionnaire is completed.</t>
-  </si>
-  <si>
-    <t>Codes 1–3 are unambiguously urban (metro areas) and codes 8–9 are unambiguously rural. However, codes 4–7 represent intermediate non-metro areas that could reasonably be classified as either urban or rural. Decision needed on cutpoint for rural vs urban</t>
   </si>
   <si>
     <t>ab13datemonth;
@@ -1214,9 +1189,6 @@
   </si>
   <si>
     <t>R13 D MARITAL STATUS AT R13</t>
-  </si>
-  <si>
-    <t>r13drucc</t>
   </si>
   <si>
     <t>R13 D METRO / NON-METRO RESIDENCE</t>
@@ -1363,19 +1335,6 @@
     <t>hw13currweigh * 0.45359237</t>
   </si>
   <si>
-    <t>case_when(
-  hw13howtallft %in% c(-7, -8, -9, -1) |
-  hw13howtallin %in% c(-7, -8, -9, -1) |
-  hw13currweigh %in% c(-7, -8, -9, -1) ~ NA_real_,
-  !is.na(hw13howtallft) &amp; !is.na(hw13howtallin) &amp; !is.na(hw13currweigh) ~ {
-    height_m &lt;- ((hw13howtallft * 12) + hw13howtallin) * 0.0254
-    weight_kg &lt;- hw13currweigh * 0.453592
-    weight_kg / (height_m^2)
-  },
-  TRUE ~ NA_real_
-)</t>
-  </si>
-  <si>
     <t>wc13wstmsrinc * 2.54</t>
   </si>
   <si>
@@ -1401,6 +1360,27 @@
 hc13disescn6 %in% c(1,7) ~ 1;
 TRUE ~ NA
 )</t>
+  </si>
+  <si>
+    <t>NHATS_R13_Final_Release_SAS; NHATS_R13_SP_Sen_Dem_STATA</t>
+  </si>
+  <si>
+    <t>r13dgender</t>
+  </si>
+  <si>
+    <t>R13 D GENDER OF SP</t>
+  </si>
+  <si>
+    <t>we don’t have access to sensitive data? As only skin cancer and general cancer declaration is given in the SP public file. To clarify</t>
+  </si>
+  <si>
+    <t>pa13dfavact</t>
+  </si>
+  <si>
+    <t>R13 D FAVORITE ACTIVITY AT R13</t>
+  </si>
+  <si>
+    <t>pa13dfavact is in text format, would be difficult to read through open text to fetch physical activity based leisure activities.</t>
   </si>
   <si>
     <t>case_when(
@@ -1418,45 +1398,47 @@
 hc13cancerty6 == 2 &amp; 
 hc13cancerty7 == 2 &amp; 
 hc13cancerty8 == 2 ~ 0;
-TRUE ~ NA_integer
+TRUE ~ NA_integer_
 )</t>
+  </si>
+  <si>
+    <t>recode(c(1,2) = 1; c(3,4,5,6) = 0; c(-9,-8,-7) = NA; -1 = NA; ELSE = NA)</t>
+  </si>
+  <si>
+    <t>Non metropolitan is not necessarily a rural area, therefore incompatible.</t>
+  </si>
+  <si>
+    <t>r13dmetnonmet</t>
+  </si>
+  <si>
+    <t>recode(3 = 1; c(1,2) = 0; c(-9,-8,-7,-1) = NA; ELSE = NA)</t>
+  </si>
+  <si>
+    <t>case_when(
+  hw13howtallft %in% c(-7, -8, -9, -1) |
+    hw13howtallin %in% c(-7, -8, -9, -1) |
+    hw13currweigh %in% c(-7, -8, -9, -1) ~ NA_real_,
+  !is.na(hw13howtallft) &amp; !is.na(hw13howtallin) &amp; !is.na(hw13currweigh) ~
+    (hw13currweigh * 0.453592) /
+    ((((hw13howtallft * 12) + hw13howtallin) * 0.0254)^2),
+  TRUE ~ NA_real_
+)</t>
+  </si>
+  <si>
+    <t>recode(5 = 1; 4 = 2; 3 = 3; c(1,2) = 4; ELSE = NA)</t>
+  </si>
+  <si>
+    <t>recode(c(1,7) = 1; 2 = 0; c(-9,-8,-7) = NA; -1 = NA; ELSE = NA)</t>
   </si>
   <si>
     <t>case_when(
 hc13trbfalbck %in% c(1,2,3) | hc13aslep30mn %in% c(1,2,3) ~ 1;
 hc13trbfalbck %in% c(4,7) &amp; hc13aslep30mn %in% c(4,5) ~ 0;
-TRUE ~ NA_integer
+TRUE ~ NA_integer_
 )</t>
   </si>
   <si>
-    <t>NHATS_R13_Final_Release_SAS; NHATS_R13_SP_Sen_Dem_STATA</t>
-  </si>
-  <si>
-    <t>undetermined</t>
-  </si>
-  <si>
-    <t>r13dgender</t>
-  </si>
-  <si>
-    <t>R13 D GENDER OF SP</t>
-  </si>
-  <si>
-    <t>we don’t have access to sensitive data? As only skin cancer and general cancer declaration is given in the SP public file. To clarify</t>
-  </si>
-  <si>
-    <t>pa13dfavact</t>
-  </si>
-  <si>
-    <t>R13 D FAVORITE ACTIVITY AT R13</t>
-  </si>
-  <si>
-    <t>pa13dfavact is in text format, would be difficult to read through open text to fetch physical activity based leisure activities.</t>
-  </si>
-  <si>
-    <t>pa13vigoractv</t>
-  </si>
-  <si>
-    <t>R13 PA24 EVER VIGOROUS ACTIVITIES</t>
+    <t>pa13vigoractv; pa13dfavact</t>
   </si>
   <si>
     <t xml:space="preserve">-9 = Missing; 
@@ -1466,19 +1448,98 @@
 1 = YES;
 2 = NO
 7 = PREVIOUSLY REPORTED
+-1 = Inapplicable
+-8 = Don't know
+-9 = Missing
+111 = Sleeping/Napping
+131 = Eating
+132 = Going out to eat
+199 = Other self-care activities
+211 = Work and work-related activities
+221 = Other income-generating activities
+241 = Volunteering
+299 = Other productive activities
+321 = Shopping for non-durable goods
+399 = Other shopping
+411 = Food and drink preparation
+434 = Outdoor maintenance
+439 = Household chores (indoor/outdoor unspecified)
+441 = Animal and pet care
+442 = Walking/exercising pets
+449 = Other animal and pet care
+451 = Vehicle maintenance and repair
+471 = Financial management
+499 = Other household activities
+511 = Physical care and assistance to others
+599 = Other physical care
+611 = Socializing in person
+612 = Socializing on the phone
+616 = Socializing/communicating on a computer
+621 = Watching TV/movies
+631 = Puzzles/games (not computer/online)
+632 = Gambling (not online/casino)
+636 = Puzzles/games (computer/online)
+641 = Arts, crafts, hobbies
+642 = Reading
+643 = Writing
+644 = Listening to music
+646 = Computer/online leisure
+651 = Smoking/tobacco use
+652 = Drinking alcohol
+661 = Doing nothing/relaxing
+669 = No activity
+699 = Other non-active leisure
+711 = Playing sports
+712 = Walking/jogging
+713 = Other outdoor recreation
+714 = Attending sporting events
+715 = Other physical activity (exercise, yoga, swimming, dancing)
+718 = Watching sporting events
+721 = Attending arts (plays, concerts)
+723 = Attending movies
+724 = Attending casinos
+737 = Leisure travel
+799 = Other active leisure
+811 = Attending religious activities
+812 = Other religious/spiritual activities
+821 = Attending meetings/events
+899 = Other organizational activity
+991 = Other miscellaneous
+992 = No favorite activity
+997 = Refused
+998 = Don't know
+999 = Not codeable
 </t>
   </si>
   <si>
-    <t>recode(
-  pa13vigoractv,
-  `1` = 1,
-  `7` = 1,
-  `2` = 0,
-  `-9` = NA_real_,
-  `-8` = NA_real_,
-  `-7` = NA_real_,
-  `-1` = NA_real_,
-  .default = NA_real_
+    <t>R12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">participant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">favourite activity considered as sports: 711 = Playing sports;
+715 = Exercise (gym, yoga, etc.) </t>
+  </si>
+  <si>
+    <t>R13 PA24 EVER VIGOROUS ACTIVITIES; R13 D FAVORITE ACTIVITY AT R13</t>
+  </si>
+  <si>
+    <t>case_when(
+  pa13vigoractv %in% c(-9, -8, -7, -1) |
+    pa13dfavact %in% c(-9, -8, -1, 997, 998, 999) ~ NA_real_,
+  pa13vigoractv == 1 |
+    pa13dfavact %in% c(711, 715) ~ 1,
+  pa13vigoractv == 2 &amp;
+    !pa13dfavact %in% c(711, 715) ~ 0,
+  TRUE ~ NA_integer_
+)</t>
+  </si>
+  <si>
+    <t>case_when(
+dt13getoplcs1 == 1 | ha13howgtstr7 == 1 ~ 1;
+dt13getoplcs1 == 2 &amp; ha13howgtstr7 == 2 ~ 0;
+TRUE ~ NA_integer_
 )</t>
   </si>
 </sst>
@@ -1602,7 +1663,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1642,14 +1703,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1991,41 +2049,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABC73F24-28B6-451D-9DE2-0CD6B57BA63C}">
   <dimension ref="A1:Y164"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="1" max="2" width="9.1328125" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="37.140625" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" customWidth="1"/>
-    <col min="8" max="8" width="25.28515625" customWidth="1"/>
-    <col min="9" max="9" width="27.85546875" customWidth="1"/>
+    <col min="4" max="4" width="37.1328125" customWidth="1"/>
+    <col min="5" max="5" width="22.3984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.73046875" customWidth="1"/>
+    <col min="8" max="8" width="25.265625" customWidth="1"/>
+    <col min="9" max="9" width="27.86328125" customWidth="1"/>
     <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="57.42578125" style="2" customWidth="1"/>
-    <col min="12" max="13" width="70.42578125" style="3" customWidth="1"/>
-    <col min="14" max="16" width="22.140625" customWidth="1"/>
-    <col min="17" max="17" width="24.5703125" customWidth="1"/>
-    <col min="18" max="19" width="31.85546875" customWidth="1"/>
-    <col min="20" max="20" width="21.140625" customWidth="1"/>
-    <col min="21" max="21" width="28.42578125" customWidth="1"/>
-    <col min="22" max="22" width="23.7109375" customWidth="1"/>
-    <col min="23" max="23" width="27.7109375" customWidth="1"/>
-    <col min="24" max="24" width="61.5703125" customWidth="1"/>
-    <col min="25" max="25" width="22.42578125" customWidth="1"/>
+    <col min="11" max="11" width="57.3984375" style="2" customWidth="1"/>
+    <col min="12" max="13" width="70.3984375" style="3" customWidth="1"/>
+    <col min="14" max="16" width="22.1328125" customWidth="1"/>
+    <col min="17" max="17" width="24.59765625" customWidth="1"/>
+    <col min="18" max="19" width="31.86328125" customWidth="1"/>
+    <col min="20" max="20" width="21.1328125" customWidth="1"/>
+    <col min="21" max="21" width="28.3984375" customWidth="1"/>
+    <col min="22" max="22" width="23.73046875" customWidth="1"/>
+    <col min="23" max="23" width="27.73046875" customWidth="1"/>
+    <col min="24" max="24" width="61.59765625" customWidth="1"/>
+    <col min="25" max="25" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>3</v>
@@ -2034,10 +2092,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>1</v>
@@ -2046,37 +2104,37 @@
         <v>5</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="N1" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="O1" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="Q1" s="13" t="s">
-        <v>279</v>
-      </c>
       <c r="R1" s="10" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="S1" s="14" t="s">
         <v>9</v>
       </c>
       <c r="T1" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="U1" s="15" t="s">
         <v>280</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>281</v>
       </c>
       <c r="V1" s="15" t="s">
         <v>6</v>
@@ -2088,15 +2146,15 @@
         <v>8</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -2111,99 +2169,99 @@
         <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K2" t="s">
         <v>283</v>
-      </c>
-      <c r="K2" t="s">
-        <v>284</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M2"/>
       <c r="N2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O2" s="16"/>
       <c r="P2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q2" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="R2" s="16"/>
       <c r="S2" s="4"/>
       <c r="U2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="W2" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K3"/>
       <c r="N3" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O3" s="16"/>
       <c r="Q3" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="U3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="V3" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="W3" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="X3" s="4">
         <v>2</v>
       </c>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -2211,29 +2269,29 @@
       <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O4" s="16"/>
       <c r="R4" s="4"/>
@@ -2242,7 +2300,7 @@
         <v>14</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>14</v>
@@ -2251,159 +2309,159 @@
         <v>14</v>
       </c>
       <c r="Y4" s="11" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="K5" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q5" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U5" t="s">
+        <v>25</v>
+      </c>
+      <c r="V5" t="s">
         <v>26</v>
       </c>
-      <c r="V5" t="s">
-        <v>27</v>
-      </c>
       <c r="W5" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="K6" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O6" s="16"/>
       <c r="P6" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q6" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="R6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="U6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="V6" s="4" t="s">
+      <c r="W6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="W6" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="X6" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="120" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O7" s="16"/>
       <c r="S7" s="2"/>
@@ -2420,335 +2478,335 @@
         <v>14</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>41</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J8" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="K8" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O8" s="16"/>
       <c r="P8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q8" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V8" t="s">
+        <v>36</v>
+      </c>
+      <c r="W8" t="s">
         <v>37</v>
       </c>
-      <c r="W8" t="s">
-        <v>38</v>
-      </c>
       <c r="X8" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="105" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J9" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="K9" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O9" s="16"/>
       <c r="P9" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q9" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
         <v>47</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
       <c r="I10" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J10" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="K10" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="N10" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O10" s="16"/>
       <c r="P10" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q10" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="R10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="U10" t="s">
+        <v>25</v>
+      </c>
+      <c r="V10" t="s">
         <v>26</v>
       </c>
-      <c r="V10" t="s">
+      <c r="W10" t="s">
         <v>27</v>
       </c>
-      <c r="W10" t="s">
-        <v>28</v>
-      </c>
       <c r="X10" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J11" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="K11" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="N11" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O11" s="16"/>
       <c r="P11" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q11" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U11" t="s">
+        <v>25</v>
+      </c>
+      <c r="V11" t="s">
         <v>26</v>
       </c>
-      <c r="V11" t="s">
+      <c r="W11" t="s">
         <v>27</v>
       </c>
-      <c r="W11" t="s">
-        <v>28</v>
-      </c>
       <c r="X11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
         <v>55</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J12" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="K12" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="L12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M12"/>
       <c r="N12" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O12" s="16"/>
       <c r="P12" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q12" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V12" t="s">
+        <v>36</v>
+      </c>
+      <c r="W12" t="s">
         <v>37</v>
       </c>
-      <c r="W12" t="s">
-        <v>38</v>
-      </c>
       <c r="X12" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="180" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="171" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
         <v>59</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I13" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J13" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="K13" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O13" s="16"/>
       <c r="U13" t="s">
         <v>14</v>
       </c>
       <c r="V13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="W13" t="s">
         <v>14</v>
@@ -2757,582 +2815,582 @@
         <v>14</v>
       </c>
       <c r="Y13" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="180" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="171" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" t="s">
         <v>63</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I14" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J14" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="K14" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O14" s="16"/>
       <c r="P14" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q14" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V14" t="s">
+        <v>36</v>
+      </c>
+      <c r="W14" t="s">
         <v>37</v>
       </c>
-      <c r="W14" t="s">
-        <v>38</v>
-      </c>
       <c r="X14" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="195" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
         <v>67</v>
       </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I15" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>342</v>
+        <v>387</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="L15" s="17"/>
+        <v>335</v>
+      </c>
+      <c r="L15" s="19"/>
       <c r="N15" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O15" s="16"/>
       <c r="P15" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q15" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>389</v>
+        <v>14</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>389</v>
+        <v>287</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>389</v>
+        <v>14</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="Y15" s="19" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="135" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="Y15" s="17" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
         <v>70</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" t="s">
         <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" t="s">
-        <v>73</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="N16" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O16" s="16"/>
       <c r="P16" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q16" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="R16" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="U16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" t="s">
         <v>76</v>
       </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N17" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O17" s="16"/>
       <c r="P17" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q17" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="V17" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="W17" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="X17" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" t="s">
         <v>79</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" t="s">
         <v>80</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" t="s">
-        <v>81</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J18" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="K18" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="N18" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O18" s="16"/>
       <c r="P18" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q18" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="R18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X18" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
         <v>83</v>
       </c>
-      <c r="D19" t="s">
-        <v>84</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I19" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N19" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O19" s="16"/>
       <c r="P19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q19" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="V19" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="W19" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="X19" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="210" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="156.75" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" t="s">
         <v>85</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G20" t="s">
-        <v>87</v>
-      </c>
       <c r="I20" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="N20" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O20" s="16"/>
       <c r="P20" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q20" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="R20" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="U20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" t="s">
         <v>88</v>
       </c>
-      <c r="D21" t="s">
-        <v>89</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J21" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="K21" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="N21" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O21" s="16"/>
       <c r="P21" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q21" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="R21" t="s">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s">
+        <v>25</v>
+      </c>
+      <c r="V21" t="s">
+        <v>36</v>
+      </c>
+      <c r="W21" t="s">
         <v>74</v>
       </c>
-      <c r="U21" t="s">
-        <v>26</v>
-      </c>
-      <c r="V21" t="s">
-        <v>37</v>
-      </c>
-      <c r="W21" t="s">
-        <v>75</v>
-      </c>
       <c r="X21" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="57" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" t="s">
         <v>90</v>
       </c>
-      <c r="D22" t="s">
-        <v>91</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I22" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J22" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="K22" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O22" s="16"/>
       <c r="P22" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q22" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U22" t="s">
+        <v>25</v>
+      </c>
+      <c r="V22" t="s">
         <v>26</v>
       </c>
-      <c r="V22" t="s">
-        <v>27</v>
-      </c>
       <c r="W22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="X22" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" t="s">
         <v>92</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F23" t="s">
-        <v>50</v>
-      </c>
-      <c r="G23" t="s">
-        <v>94</v>
-      </c>
       <c r="I23" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J23" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N23" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O23" s="16"/>
       <c r="P23" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" t="s">
         <v>95</v>
       </c>
-      <c r="D24" t="s">
-        <v>96</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
       </c>
       <c r="I24" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N24" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O24" s="16"/>
       <c r="U24" s="4" t="s">
@@ -3348,36 +3406,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" t="s">
         <v>97</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" t="s">
         <v>99</v>
       </c>
-      <c r="F25" t="s">
-        <v>50</v>
-      </c>
-      <c r="G25" t="s">
-        <v>100</v>
-      </c>
       <c r="I25" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J25" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N25" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O25" s="16"/>
       <c r="U25" s="4" t="s">
@@ -3393,36 +3451,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" t="s">
         <v>101</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="F26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I26" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J26" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N26" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O26" s="16"/>
       <c r="U26" s="4" t="s">
@@ -3438,36 +3496,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" t="s">
         <v>104</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" t="s">
         <v>105</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G27" t="s">
-        <v>106</v>
-      </c>
       <c r="I27" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N27" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O27" s="16"/>
       <c r="U27" s="4" t="s">
@@ -3483,37 +3541,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" t="s">
         <v>107</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" t="s">
         <v>108</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" t="s">
-        <v>50</v>
-      </c>
-      <c r="G28" t="s">
-        <v>109</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J28" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N28" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O28" s="16"/>
       <c r="U28" s="4" t="s">
@@ -3529,36 +3587,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
         <v>110</v>
       </c>
-      <c r="D29" t="s">
-        <v>111</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I29" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N29" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O29" s="16"/>
       <c r="U29" s="4" t="s">
@@ -3574,36 +3632,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C30" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" t="s">
         <v>113</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F30" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" t="s">
         <v>114</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" t="s">
-        <v>50</v>
-      </c>
-      <c r="G30" t="s">
-        <v>115</v>
-      </c>
       <c r="I30" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N30" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O30" s="16"/>
       <c r="U30" s="4" t="s">
@@ -3619,36 +3677,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C31" t="s">
+        <v>115</v>
+      </c>
+      <c r="D31" t="s">
         <v>116</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" t="s">
         <v>117</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F31" t="s">
-        <v>50</v>
-      </c>
-      <c r="G31" t="s">
-        <v>118</v>
-      </c>
       <c r="I31" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N31" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O31" s="16"/>
       <c r="U31" s="4" t="s">
@@ -3664,36 +3722,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C32" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" t="s">
         <v>119</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F32" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F32" t="s">
-        <v>50</v>
-      </c>
-      <c r="G32" t="s">
-        <v>121</v>
-      </c>
       <c r="I32" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N32" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O32" s="16"/>
       <c r="U32" s="4" t="s">
@@ -3709,36 +3767,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" t="s">
         <v>122</v>
       </c>
-      <c r="D33" t="s">
-        <v>123</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I33" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J33" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N33" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O33" s="16"/>
       <c r="U33" s="4" t="s">
@@ -3754,36 +3812,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" t="s">
         <v>124</v>
       </c>
-      <c r="D34" t="s">
-        <v>125</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I34" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N34" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O34" s="16"/>
       <c r="U34" s="4" t="s">
@@ -3799,36 +3857,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C35" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" t="s">
         <v>126</v>
       </c>
-      <c r="D35" t="s">
-        <v>127</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I35" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J35" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N35" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O35" s="16"/>
       <c r="U35" s="4" t="s">
@@ -3844,36 +3902,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C36" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" t="s">
         <v>128</v>
       </c>
-      <c r="D36" t="s">
-        <v>129</v>
-      </c>
       <c r="E36" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I36" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J36" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N36" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O36" s="16"/>
       <c r="U36" s="4" t="s">
@@ -3889,36 +3947,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C37" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" t="s">
         <v>130</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37" t="s">
         <v>131</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F37" t="s">
-        <v>50</v>
-      </c>
-      <c r="G37" t="s">
-        <v>132</v>
-      </c>
       <c r="I37" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J37" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N37" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O37" s="16"/>
       <c r="U37" s="4" t="s">
@@ -3934,37 +3992,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C38" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" t="s">
         <v>133</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" t="s">
+        <v>49</v>
+      </c>
+      <c r="G38" t="s">
         <v>135</v>
-      </c>
-      <c r="F38" t="s">
-        <v>50</v>
-      </c>
-      <c r="G38" t="s">
-        <v>136</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J38" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N38" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O38" s="16"/>
       <c r="U38" s="4" t="s">
@@ -3980,38 +4038,38 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:25" s="2" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" s="2" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I39" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J39" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O39" s="16"/>
       <c r="P39"/>
@@ -4031,37 +4089,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C40" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" t="s">
         <v>141</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="F40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J40" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N40" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O40" s="16"/>
       <c r="U40" s="4" t="s">
@@ -4077,36 +4135,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C41" t="s">
+        <v>143</v>
+      </c>
+      <c r="D41" t="s">
         <v>144</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I41" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N41" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O41" s="16"/>
       <c r="U41" s="4" t="s">
@@ -4122,36 +4180,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" t="s">
         <v>147</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" t="s">
         <v>148</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F42" t="s">
-        <v>50</v>
-      </c>
-      <c r="G42" t="s">
-        <v>149</v>
-      </c>
       <c r="I42" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N42" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O42" s="16"/>
       <c r="U42" s="4" t="s">
@@ -4167,37 +4225,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C43" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" t="s">
         <v>150</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="F43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G43" t="s">
         <v>152</v>
-      </c>
-      <c r="F43" t="s">
-        <v>50</v>
-      </c>
-      <c r="G43" t="s">
-        <v>153</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N43" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O43" s="16"/>
       <c r="U43" s="4" t="s">
@@ -4213,36 +4271,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="57" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C44" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" t="s">
         <v>154</v>
       </c>
-      <c r="D44" t="s">
-        <v>155</v>
-      </c>
       <c r="E44" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I44" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J44" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N44" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O44" s="16"/>
       <c r="U44" s="4" t="s">
@@ -4258,43 +4316,43 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="105" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C45" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" t="s">
         <v>157</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="F45" t="s">
         <v>16</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I45" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J45" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="K45" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="M45" s="5"/>
       <c r="N45" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O45" s="16"/>
       <c r="S45" s="2"/>
@@ -4302,7 +4360,7 @@
         <v>14</v>
       </c>
       <c r="V45" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="W45" s="4" t="s">
         <v>14</v>
@@ -4311,53 +4369,53 @@
         <v>14</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" ht="75" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C46" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" t="s">
         <v>161</v>
       </c>
-      <c r="D46" t="s">
-        <v>162</v>
-      </c>
       <c r="E46" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
       </c>
       <c r="H46" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I46" t="s">
+        <v>377</v>
+      </c>
+      <c r="J46" t="s">
+        <v>348</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="L46" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="I46" t="s">
-        <v>388</v>
-      </c>
-      <c r="J46" t="s">
-        <v>356</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="L46" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="M46" s="5"/>
       <c r="N46" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O46" s="16"/>
       <c r="U46" t="s">
         <v>14</v>
       </c>
       <c r="V46" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>14</v>
@@ -4366,337 +4424,337 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C47" t="s">
+        <v>164</v>
+      </c>
+      <c r="D47" t="s">
         <v>165</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F47" t="s">
+        <v>49</v>
+      </c>
+      <c r="G47" t="s">
         <v>166</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F47" t="s">
-        <v>50</v>
-      </c>
-      <c r="G47" t="s">
-        <v>167</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J47" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="K47" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M47" s="5"/>
       <c r="N47" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O47" s="16"/>
       <c r="P47" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q47" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" ht="135" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C48" t="s">
+        <v>167</v>
+      </c>
+      <c r="D48" t="s">
         <v>168</v>
       </c>
-      <c r="D48" t="s">
-        <v>169</v>
-      </c>
       <c r="E48" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I48" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J48" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="K48" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M48" s="5"/>
       <c r="N48" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O48" s="16"/>
       <c r="P48" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q48" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V48" t="s">
+        <v>36</v>
+      </c>
+      <c r="W48" t="s">
         <v>37</v>
       </c>
-      <c r="W48" t="s">
-        <v>38</v>
-      </c>
       <c r="X48" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" ht="225" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" ht="213.75" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C49" t="s">
+        <v>170</v>
+      </c>
+      <c r="D49" t="s">
         <v>171</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I49" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J49" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M49" s="5"/>
       <c r="N49" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O49" s="16"/>
       <c r="P49" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q49" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="S49" s="2"/>
       <c r="U49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" ht="225" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" ht="213.75" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C50" t="s">
+        <v>174</v>
+      </c>
+      <c r="D50" t="s">
         <v>175</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I50" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J50" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M50" s="5"/>
       <c r="N50" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O50" s="16"/>
       <c r="P50" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q50" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="S50" s="2"/>
       <c r="U50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" ht="105" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C51" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51" t="s">
         <v>178</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I51" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J51" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="K51" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="L51" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M51" s="5"/>
       <c r="N51" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O51" s="16"/>
       <c r="P51" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q51" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" ht="120" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D52" t="s">
         <v>182</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I52" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J52" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O52" s="16"/>
       <c r="U52" s="4" t="s">
@@ -4712,97 +4770,97 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="285" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="270.75" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C53" t="s">
+        <v>185</v>
+      </c>
+      <c r="D53" t="s">
         <v>186</v>
       </c>
-      <c r="D53" t="s">
-        <v>187</v>
-      </c>
       <c r="E53" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I53" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="L53" s="5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M53" s="5"/>
       <c r="N53" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O53" s="16"/>
       <c r="P53" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q53" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C54" t="s">
+        <v>187</v>
+      </c>
+      <c r="D54" t="s">
         <v>188</v>
       </c>
-      <c r="D54" t="s">
-        <v>189</v>
-      </c>
       <c r="E54" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I54" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J54" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N54" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O54" s="16"/>
       <c r="U54" s="4" t="s">
@@ -4818,38 +4876,38 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C55" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" t="s">
         <v>190</v>
       </c>
-      <c r="D55" t="s">
-        <v>191</v>
-      </c>
       <c r="E55" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I55" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J55" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O55" s="16"/>
       <c r="U55" s="4" t="s">
@@ -4865,38 +4923,38 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C56" t="s">
+        <v>191</v>
+      </c>
+      <c r="D56" t="s">
         <v>192</v>
       </c>
-      <c r="D56" t="s">
-        <v>193</v>
-      </c>
       <c r="E56" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I56" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J56" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O56" s="16"/>
       <c r="U56" s="4" t="s">
@@ -4912,36 +4970,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C57" t="s">
+        <v>193</v>
+      </c>
+      <c r="D57" t="s">
         <v>194</v>
       </c>
-      <c r="D57" t="s">
-        <v>195</v>
-      </c>
       <c r="E57" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I57" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J57" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N57" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O57" s="16"/>
       <c r="U57" s="4" t="s">
@@ -4957,36 +5015,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="57" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C58" t="s">
+        <v>195</v>
+      </c>
+      <c r="D58" t="s">
         <v>196</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I58" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J58" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N58" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O58" s="16"/>
       <c r="U58" s="4" t="s">
@@ -5002,33 +5060,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C59" t="s">
+        <v>198</v>
+      </c>
+      <c r="D59" t="s">
         <v>199</v>
       </c>
-      <c r="D59" t="s">
-        <v>200</v>
-      </c>
       <c r="E59" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
       </c>
       <c r="I59" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J59" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N59" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O59" s="16"/>
       <c r="U59" s="4" t="s">
@@ -5044,33 +5102,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C60" t="s">
+        <v>200</v>
+      </c>
+      <c r="D60" t="s">
         <v>201</v>
       </c>
-      <c r="D60" t="s">
-        <v>202</v>
-      </c>
       <c r="E60" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
       </c>
       <c r="I60" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N60" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O60" s="16"/>
       <c r="U60" s="4" t="s">
@@ -5086,33 +5144,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C61" t="s">
+        <v>202</v>
+      </c>
+      <c r="D61" t="s">
         <v>203</v>
       </c>
-      <c r="D61" t="s">
-        <v>204</v>
-      </c>
       <c r="E61" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
       </c>
       <c r="I61" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J61" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N61" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O61" s="16"/>
       <c r="U61" s="4" t="s">
@@ -5128,33 +5186,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D62" t="s">
         <v>205</v>
       </c>
-      <c r="D62" t="s">
-        <v>206</v>
-      </c>
       <c r="E62" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F62" t="s">
         <v>16</v>
       </c>
       <c r="I62" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J62" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N62" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O62" s="16"/>
       <c r="U62" s="4" t="s">
@@ -5170,33 +5228,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C63" t="s">
+        <v>206</v>
+      </c>
+      <c r="D63" t="s">
         <v>207</v>
       </c>
-      <c r="D63" t="s">
-        <v>208</v>
-      </c>
       <c r="E63" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F63" t="s">
         <v>16</v>
       </c>
       <c r="I63" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J63" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N63" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O63" s="16"/>
       <c r="S63" s="2"/>
@@ -5214,33 +5272,33 @@
       </c>
       <c r="Y63" s="2"/>
     </row>
-    <row r="64" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C64" t="s">
+        <v>208</v>
+      </c>
+      <c r="D64" t="s">
         <v>209</v>
       </c>
-      <c r="D64" t="s">
-        <v>210</v>
-      </c>
       <c r="E64" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
       </c>
       <c r="I64" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J64" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N64" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O64" s="16"/>
       <c r="U64" s="4" t="s">
@@ -5256,34 +5314,34 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C65" t="s">
+        <v>210</v>
+      </c>
+      <c r="D65" t="s">
         <v>211</v>
       </c>
-      <c r="D65" t="s">
-        <v>212</v>
-      </c>
       <c r="E65" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N65" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O65" s="16"/>
       <c r="U65" s="4" t="s">
@@ -5299,97 +5357,97 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="105" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C66" t="s">
+        <v>212</v>
+      </c>
+      <c r="D66" t="s">
         <v>213</v>
       </c>
-      <c r="D66" t="s">
-        <v>214</v>
-      </c>
       <c r="E66" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F66" t="s">
         <v>16</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I66" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J66" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="K66" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M66" s="5"/>
       <c r="N66" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O66" s="16"/>
       <c r="P66" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q66" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="S66" s="2"/>
       <c r="U66" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V66" t="s">
+        <v>36</v>
+      </c>
+      <c r="W66" t="s">
         <v>37</v>
       </c>
-      <c r="W66" t="s">
-        <v>38</v>
-      </c>
       <c r="X66" s="2" t="s">
-        <v>311</v>
+        <v>391</v>
       </c>
       <c r="Y66" s="2"/>
     </row>
-    <row r="67" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C67" t="s">
+        <v>215</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="E67" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F67" t="s">
+        <v>49</v>
+      </c>
+      <c r="G67" t="s">
         <v>217</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F67" t="s">
-        <v>50</v>
-      </c>
-      <c r="G67" t="s">
-        <v>218</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J67" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N67" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O67" s="16"/>
       <c r="U67" s="4" t="s">
@@ -5405,36 +5463,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="135" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C68" t="s">
+        <v>218</v>
+      </c>
+      <c r="D68" t="s">
         <v>219</v>
       </c>
-      <c r="D68" t="s">
-        <v>220</v>
-      </c>
       <c r="E68" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I68" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J68" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N68" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O68" s="16"/>
       <c r="U68" s="4" t="s">
@@ -5450,94 +5508,94 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="150" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="142.5" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C69" t="s">
+        <v>221</v>
+      </c>
+      <c r="D69" t="s">
         <v>222</v>
       </c>
-      <c r="D69" t="s">
-        <v>223</v>
-      </c>
       <c r="E69" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F69" t="s">
         <v>16</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I69" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J69" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="L69" s="5" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="M69" s="5"/>
       <c r="N69" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O69" s="16"/>
       <c r="P69" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q69" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W69" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C70" t="s">
+        <v>224</v>
+      </c>
+      <c r="D70" t="s">
         <v>225</v>
       </c>
-      <c r="D70" t="s">
-        <v>226</v>
-      </c>
       <c r="E70" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F70" t="s">
         <v>16</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I70" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J70" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N70" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O70" s="16"/>
       <c r="U70" s="4" t="s">
@@ -5553,36 +5611,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C71" t="s">
+        <v>227</v>
+      </c>
+      <c r="D71" t="s">
         <v>228</v>
       </c>
-      <c r="D71" t="s">
-        <v>229</v>
-      </c>
       <c r="E71" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I71" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J71" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N71" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O71" s="16"/>
       <c r="U71" s="4" t="s">
@@ -5598,34 +5656,34 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C72" t="s">
+        <v>229</v>
+      </c>
+      <c r="D72" t="s">
         <v>230</v>
       </c>
-      <c r="D72" t="s">
-        <v>231</v>
-      </c>
       <c r="E72" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F72" t="s">
         <v>16</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J72" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N72" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O72" s="16"/>
       <c r="U72" s="4" t="s">
@@ -5641,36 +5699,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="216" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="216" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C73" t="s">
+        <v>231</v>
+      </c>
+      <c r="D73" t="s">
         <v>232</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="F73" t="s">
         <v>16</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I73" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J73" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N73" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O73" s="16"/>
       <c r="U73" s="4" t="s">
@@ -5686,36 +5744,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C74" t="s">
+        <v>235</v>
+      </c>
+      <c r="D74" t="s">
         <v>236</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I74" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N74" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O74" s="16"/>
       <c r="U74" s="4" t="s">
@@ -5731,36 +5789,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="57" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C75" t="s">
+        <v>239</v>
+      </c>
+      <c r="D75" t="s">
         <v>240</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="F75" t="s">
         <v>16</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I75" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J75" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N75" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O75" s="16"/>
       <c r="U75" s="4" t="s">
@@ -5776,37 +5834,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C76" t="s">
+        <v>243</v>
+      </c>
+      <c r="D76" t="s">
         <v>244</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="F76" t="s">
         <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J76" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N76" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O76" s="16"/>
       <c r="S76" s="2"/>
@@ -5824,36 +5882,36 @@
       </c>
       <c r="Y76" s="2"/>
     </row>
-    <row r="77" spans="1:25" ht="165" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="142.5" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C77" t="s">
+        <v>246</v>
+      </c>
+      <c r="D77" t="s">
         <v>247</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="F77" t="s">
         <v>16</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I77" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J77" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N77" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O77" s="16"/>
       <c r="U77" s="4" t="s">
@@ -5869,36 +5927,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C78" t="s">
+        <v>250</v>
+      </c>
+      <c r="D78" t="s">
         <v>251</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I78" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J78" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N78" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O78" s="16"/>
       <c r="U78" s="4" t="s">
@@ -5914,36 +5972,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="120" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C79" t="s">
+        <v>254</v>
+      </c>
+      <c r="D79" t="s">
         <v>255</v>
       </c>
-      <c r="D79" t="s">
-        <v>256</v>
-      </c>
       <c r="E79" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F79" t="s">
         <v>16</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I79" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J79" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N79" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O79" s="16"/>
       <c r="U79" s="4" t="s">
@@ -5959,175 +6017,177 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="165" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C80" t="s">
+        <v>257</v>
+      </c>
+      <c r="D80" t="s">
         <v>258</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="F80" t="s">
         <v>16</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I80" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J80" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="K80" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="M80" s="5"/>
       <c r="N80" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="O80" s="16"/>
       <c r="P80" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q80" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="S80" s="2"/>
       <c r="U80" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V80" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W80" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="Y80" s="2"/>
-    </row>
-    <row r="81" spans="1:25" ht="105" x14ac:dyDescent="0.25">
+      <c r="Y80" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C81" t="s">
+        <v>260</v>
+      </c>
+      <c r="D81" t="s">
         <v>261</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="F81" t="s">
         <v>16</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I81" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J81" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="K81" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L81" s="5" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="M81" s="5"/>
       <c r="N81" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O81" s="16"/>
       <c r="P81" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q81" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V81" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W81" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="82" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C82" t="s">
+        <v>263</v>
+      </c>
+      <c r="D82" t="s">
         <v>264</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="F82" t="s">
         <v>16</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I82" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="L82" s="20"/>
+        <v>382</v>
+      </c>
+      <c r="L82" s="5"/>
       <c r="M82" s="5" t="s">
         <v>13</v>
       </c>
       <c r="N82" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O82" s="16"/>
       <c r="P82" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q82" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="S82" s="2"/>
       <c r="U82" t="s">
         <v>14</v>
       </c>
       <c r="V82" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="W82" t="s">
         <v>14</v>
@@ -6136,36 +6196,36 @@
         <v>14</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="83" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C83" t="s">
+        <v>266</v>
+      </c>
+      <c r="D83" t="s">
         <v>267</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="F83" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I83" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N83" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O83" s="16"/>
       <c r="U83" s="4" t="s">
@@ -6181,38 +6241,38 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C84" t="s">
+        <v>269</v>
+      </c>
+      <c r="D84" t="s">
         <v>270</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="F84" t="s">
         <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I84" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
       <c r="N84" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="O84" s="16"/>
       <c r="U84" s="4" t="s">
@@ -6228,172 +6288,172 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.45">
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.45">
       <c r="L88" s="8"/>
       <c r="M88" s="8"/>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.45">
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.45">
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.45">
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.45">
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="L96" s="5"/>
       <c r="M96" s="5"/>
     </row>
-    <row r="97" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="97" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
     </row>
-    <row r="99" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="99" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="W99" s="9"/>
       <c r="X99" s="9"/>
     </row>
-    <row r="101" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="101" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
     </row>
-    <row r="102" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="102" spans="8:24" x14ac:dyDescent="0.45">
       <c r="J102" s="2"/>
     </row>
-    <row r="103" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="103" spans="8:24" x14ac:dyDescent="0.45">
       <c r="J103" s="2"/>
     </row>
-    <row r="104" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="104" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
     </row>
-    <row r="111" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="111" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
     </row>
-    <row r="121" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="8:9" x14ac:dyDescent="0.45">
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
     </row>
-    <row r="123" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="8:9" x14ac:dyDescent="0.45">
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
     </row>
-    <row r="126" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="8:9" x14ac:dyDescent="0.45">
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
     </row>
-    <row r="127" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:9" x14ac:dyDescent="0.45">
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
     </row>
-    <row r="128" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="8:9" x14ac:dyDescent="0.45">
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
     </row>
-    <row r="130" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
       <c r="L130" s="5"/>
       <c r="M130" s="5"/>
     </row>
-    <row r="131" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
     </row>
-    <row r="132" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
     </row>
-    <row r="133" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
     </row>
-    <row r="134" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
     </row>
-    <row r="135" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
     </row>
-    <row r="136" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
     </row>
-    <row r="137" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
     </row>
-    <row r="138" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
     </row>
-    <row r="139" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
     </row>
-    <row r="140" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
       <c r="L140" s="8"/>
       <c r="M140" s="8"/>
     </row>
-    <row r="148" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="148" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
       <c r="L148" s="8"/>
       <c r="M148" s="8"/>
     </row>
-    <row r="150" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="150" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
     </row>
-    <row r="151" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="151" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
     </row>
-    <row r="152" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="152" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
     </row>
-    <row r="153" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="153" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
     </row>
-    <row r="154" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="154" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
     </row>
-    <row r="155" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="155" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
     </row>
-    <row r="156" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="156" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
     </row>
-    <row r="157" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="157" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
     </row>
-    <row r="159" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="159" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
       <c r="L159" s="5"/>
@@ -6401,25 +6461,25 @@
       <c r="W159" s="9"/>
       <c r="X159" s="9"/>
     </row>
-    <row r="160" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="160" spans="8:24" x14ac:dyDescent="0.45">
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
       <c r="L160" s="5"/>
       <c r="M160" s="5"/>
     </row>
-    <row r="161" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
     </row>
-    <row r="162" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
     </row>
-    <row r="163" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
     </row>
-    <row r="164" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="8:13" x14ac:dyDescent="0.45">
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
       <c r="L164" s="5"/>

--- a/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17bc974f5891b333/Documents/ProPASS/Harmo/NHATS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="8_{B04BC2F6-0886-423B-9CF8-2AF8452D03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32DD84DE-0198-46E0-8A8F-FA88CCBB9112}"/>
+  <xr:revisionPtr revIDLastSave="160" documentId="8_{B04BC2F6-0886-423B-9CF8-2AF8452D03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3921F31C-8E7E-479F-8418-8CCBAC8E8062}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F744FAC3-0BAB-4C7A-92B3-0824573F48DB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F744FAC3-0BAB-4C7A-92B3-0824573F48DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="401">
   <si>
     <t>index</t>
   </si>
@@ -1152,10 +1152,6 @@
   <si>
     <t>R13 AB COVER DATE MONTH;
 R13 AB COVER DATE YEAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r13dintvwrage
-</t>
   </si>
   <si>
     <t>R13 D AGE OF SP AT INTERVIEW</t>
@@ -1541,6 +1537,9 @@
 dt13getoplcs1 == 2 &amp; ha13howgtstr7 == 2 ~ 0;
 TRUE ~ NA_integer_
 )</t>
+  </si>
+  <si>
+    <t>r13dintvwrage</t>
   </si>
 </sst>
 </file>
@@ -1663,7 +1662,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1703,11 +1702,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2169,7 +2163,7 @@
         <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J2" t="s">
         <v>282</v>
@@ -2182,14 +2176,14 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O2" s="16"/>
       <c r="P2" t="s">
         <v>309</v>
       </c>
       <c r="Q2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R2" s="16"/>
       <c r="S2" s="4"/>
@@ -2227,18 +2221,18 @@
         <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J3" t="s">
         <v>290</v>
       </c>
       <c r="K3"/>
       <c r="N3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O3" s="16"/>
       <c r="Q3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
@@ -2280,7 +2274,7 @@
       </c>
       <c r="H4" s="2"/>
       <c r="I4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>321</v>
@@ -2291,7 +2285,7 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O4" s="16"/>
       <c r="R4" s="4"/>
@@ -2335,27 +2329,27 @@
         <v>24</v>
       </c>
       <c r="I5" t="s">
+        <v>376</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" t="s">
         <v>378</v>
-      </c>
-      <c r="K5" t="s">
-        <v>379</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>284</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" t="s">
         <v>309</v>
       </c>
       <c r="Q5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U5" t="s">
         <v>25</v>
@@ -2394,25 +2388,27 @@
       </c>
       <c r="H6" s="2"/>
       <c r="I6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="K6" t="s">
         <v>323</v>
       </c>
-      <c r="K6" t="s">
-        <v>324</v>
-      </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="N6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O6" s="16"/>
       <c r="P6" t="s">
         <v>309</v>
       </c>
       <c r="Q6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R6" t="s">
         <v>31</v>
@@ -2453,7 +2449,7 @@
         <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J7" t="s">
         <v>290</v>
@@ -2461,7 +2457,7 @@
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O7" s="16"/>
       <c r="S7" s="2"/>
@@ -2504,27 +2500,27 @@
         <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J8" t="s">
+        <v>324</v>
+      </c>
+      <c r="K8" t="s">
         <v>325</v>
-      </c>
-      <c r="K8" t="s">
-        <v>326</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>289</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O8" s="16"/>
       <c r="P8" t="s">
         <v>309</v>
       </c>
       <c r="Q8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U8" t="s">
         <v>25</v>
@@ -2562,27 +2558,27 @@
         <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J9" t="s">
+        <v>326</v>
+      </c>
+      <c r="K9" t="s">
         <v>327</v>
-      </c>
-      <c r="K9" t="s">
-        <v>328</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>300</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O9" s="16"/>
       <c r="P9" t="s">
         <v>309</v>
       </c>
       <c r="Q9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U9" s="4" t="s">
         <v>25</v>
@@ -2594,7 +2590,7 @@
         <v>50</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -2617,23 +2613,23 @@
         <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J10" t="s">
+        <v>328</v>
+      </c>
+      <c r="K10" t="s">
         <v>329</v>
       </c>
-      <c r="K10" t="s">
-        <v>330</v>
-      </c>
       <c r="N10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O10" s="16"/>
       <c r="P10" t="s">
         <v>309</v>
       </c>
       <c r="Q10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R10" t="s">
         <v>291</v>
@@ -2671,26 +2667,26 @@
         <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J11" t="s">
+        <v>330</v>
+      </c>
+      <c r="K11" t="s">
         <v>331</v>
-      </c>
-      <c r="K11" t="s">
-        <v>332</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="N11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O11" s="16"/>
       <c r="P11" t="s">
         <v>309</v>
       </c>
       <c r="Q11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U11" t="s">
         <v>25</v>
@@ -2728,27 +2724,27 @@
         <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J12" t="s">
+        <v>324</v>
+      </c>
+      <c r="K12" t="s">
         <v>325</v>
-      </c>
-      <c r="K12" t="s">
-        <v>326</v>
       </c>
       <c r="L12" t="s">
         <v>289</v>
       </c>
       <c r="M12"/>
       <c r="N12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O12" s="16"/>
       <c r="P12" t="s">
         <v>309</v>
       </c>
       <c r="Q12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U12" t="s">
         <v>25</v>
@@ -2760,7 +2756,7 @@
         <v>37</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="171" x14ac:dyDescent="0.45">
@@ -2786,20 +2782,20 @@
         <v>61</v>
       </c>
       <c r="I13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J13" t="s">
+        <v>332</v>
+      </c>
+      <c r="K13" t="s">
         <v>333</v>
-      </c>
-      <c r="K13" t="s">
-        <v>334</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>292</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O13" s="16"/>
       <c r="U13" t="s">
@@ -2841,27 +2837,27 @@
         <v>65</v>
       </c>
       <c r="I14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J14" t="s">
+        <v>332</v>
+      </c>
+      <c r="K14" t="s">
         <v>333</v>
-      </c>
-      <c r="K14" t="s">
-        <v>334</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>292</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O14" s="16"/>
       <c r="P14" t="s">
         <v>309</v>
       </c>
       <c r="Q14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U14" t="s">
         <v>25</v>
@@ -2873,7 +2869,7 @@
         <v>37</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -2899,24 +2895,23 @@
         <v>68</v>
       </c>
       <c r="I15" t="s">
-        <v>377</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>387</v>
+        <v>376</v>
+      </c>
+      <c r="J15" t="s">
+        <v>386</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="L15" s="19"/>
+        <v>334</v>
+      </c>
       <c r="N15" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O15" s="16"/>
       <c r="P15" t="s">
         <v>309</v>
       </c>
       <c r="Q15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U15" s="4" t="s">
         <v>14</v>
@@ -2930,8 +2925,8 @@
       <c r="X15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Y15" s="17" t="s">
-        <v>386</v>
+      <c r="Y15" s="11" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
@@ -2958,26 +2953,26 @@
       </c>
       <c r="H16" s="2"/>
       <c r="I16" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J16" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>295</v>
       </c>
       <c r="N16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O16" s="16"/>
       <c r="P16" t="s">
         <v>309</v>
       </c>
       <c r="Q16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R16" t="s">
         <v>294</v>
@@ -2992,7 +2987,7 @@
         <v>74</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
@@ -3018,20 +3013,20 @@
         <v>77</v>
       </c>
       <c r="I17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J17" t="s">
         <v>290</v>
       </c>
       <c r="N17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O17" s="16"/>
       <c r="P17" t="s">
         <v>309</v>
       </c>
       <c r="Q17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U17" s="4" t="s">
         <v>25</v>
@@ -3070,23 +3065,23 @@
       </c>
       <c r="H18" s="2"/>
       <c r="I18" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J18" t="s">
+        <v>337</v>
+      </c>
+      <c r="K18" t="s">
         <v>338</v>
       </c>
-      <c r="K18" t="s">
-        <v>339</v>
-      </c>
       <c r="N18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O18" s="16"/>
       <c r="P18" t="s">
         <v>309</v>
       </c>
       <c r="Q18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R18" t="s">
         <v>81</v>
@@ -3101,7 +3096,7 @@
         <v>74</v>
       </c>
       <c r="X18" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
@@ -3127,20 +3122,20 @@
         <v>77</v>
       </c>
       <c r="I19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J19" t="s">
         <v>290</v>
       </c>
       <c r="N19" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O19" s="16"/>
       <c r="P19" t="s">
         <v>309</v>
       </c>
       <c r="Q19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U19" s="4" t="s">
         <v>25</v>
@@ -3178,23 +3173,23 @@
         <v>86</v>
       </c>
       <c r="I20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J20" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>341</v>
-      </c>
       <c r="N20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O20" s="16"/>
       <c r="P20" t="s">
         <v>309</v>
       </c>
       <c r="Q20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R20" t="s">
         <v>297</v>
@@ -3209,7 +3204,7 @@
         <v>74</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.45">
@@ -3236,23 +3231,23 @@
       </c>
       <c r="H21" s="2"/>
       <c r="I21" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J21" t="s">
+        <v>341</v>
+      </c>
+      <c r="K21" t="s">
         <v>342</v>
       </c>
-      <c r="K21" t="s">
-        <v>343</v>
-      </c>
       <c r="N21" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O21" s="16"/>
       <c r="P21" t="s">
         <v>309</v>
       </c>
       <c r="Q21" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R21" t="s">
         <v>73</v>
@@ -3267,7 +3262,7 @@
         <v>74</v>
       </c>
       <c r="X21" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="57" x14ac:dyDescent="0.45">
@@ -3293,27 +3288,27 @@
         <v>77</v>
       </c>
       <c r="I22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J22" t="s">
+        <v>343</v>
+      </c>
+      <c r="K22" t="s">
         <v>344</v>
-      </c>
-      <c r="K22" t="s">
-        <v>345</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>298</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O22" s="16"/>
       <c r="P22" t="s">
         <v>309</v>
       </c>
       <c r="Q22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U22" t="s">
         <v>25</v>
@@ -3351,13 +3346,13 @@
         <v>93</v>
       </c>
       <c r="I23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J23" t="s">
         <v>290</v>
       </c>
       <c r="N23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O23" s="16"/>
       <c r="P23" t="s">
@@ -3384,13 +3379,13 @@
         <v>13</v>
       </c>
       <c r="I24" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J24" t="s">
         <v>290</v>
       </c>
       <c r="N24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O24" s="16"/>
       <c r="U24" s="4" t="s">
@@ -3429,13 +3424,13 @@
         <v>99</v>
       </c>
       <c r="I25" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J25" t="s">
         <v>290</v>
       </c>
       <c r="N25" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O25" s="16"/>
       <c r="U25" s="4" t="s">
@@ -3474,13 +3469,13 @@
         <v>99</v>
       </c>
       <c r="I26" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J26" t="s">
         <v>290</v>
       </c>
       <c r="N26" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O26" s="16"/>
       <c r="U26" s="4" t="s">
@@ -3519,13 +3514,13 @@
         <v>105</v>
       </c>
       <c r="I27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J27" t="s">
         <v>290</v>
       </c>
       <c r="N27" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O27" s="16"/>
       <c r="U27" s="4" t="s">
@@ -3565,13 +3560,13 @@
       </c>
       <c r="H28" s="2"/>
       <c r="I28" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J28" t="s">
         <v>290</v>
       </c>
       <c r="N28" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O28" s="16"/>
       <c r="U28" s="4" t="s">
@@ -3610,13 +3605,13 @@
         <v>111</v>
       </c>
       <c r="I29" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J29" t="s">
         <v>290</v>
       </c>
       <c r="N29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O29" s="16"/>
       <c r="U29" s="4" t="s">
@@ -3655,13 +3650,13 @@
         <v>114</v>
       </c>
       <c r="I30" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J30" t="s">
         <v>290</v>
       </c>
       <c r="N30" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O30" s="16"/>
       <c r="U30" s="4" t="s">
@@ -3700,13 +3695,13 @@
         <v>117</v>
       </c>
       <c r="I31" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J31" t="s">
         <v>290</v>
       </c>
       <c r="N31" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O31" s="16"/>
       <c r="U31" s="4" t="s">
@@ -3745,13 +3740,13 @@
         <v>120</v>
       </c>
       <c r="I32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J32" t="s">
         <v>290</v>
       </c>
       <c r="N32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O32" s="16"/>
       <c r="U32" s="4" t="s">
@@ -3790,13 +3785,13 @@
         <v>120</v>
       </c>
       <c r="I33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J33" t="s">
         <v>290</v>
       </c>
       <c r="N33" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O33" s="16"/>
       <c r="U33" s="4" t="s">
@@ -3835,13 +3830,13 @@
         <v>120</v>
       </c>
       <c r="I34" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J34" t="s">
         <v>290</v>
       </c>
       <c r="N34" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O34" s="16"/>
       <c r="U34" s="4" t="s">
@@ -3880,13 +3875,13 @@
         <v>120</v>
       </c>
       <c r="I35" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J35" t="s">
         <v>290</v>
       </c>
       <c r="N35" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O35" s="16"/>
       <c r="U35" s="4" t="s">
@@ -3925,13 +3920,13 @@
         <v>120</v>
       </c>
       <c r="I36" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J36" t="s">
         <v>290</v>
       </c>
       <c r="N36" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O36" s="16"/>
       <c r="U36" s="4" t="s">
@@ -3970,13 +3965,13 @@
         <v>131</v>
       </c>
       <c r="I37" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J37" t="s">
         <v>290</v>
       </c>
       <c r="N37" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O37" s="16"/>
       <c r="U37" s="4" t="s">
@@ -4016,13 +4011,13 @@
       </c>
       <c r="H38" s="2"/>
       <c r="I38" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J38" t="s">
         <v>290</v>
       </c>
       <c r="N38" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O38" s="16"/>
       <c r="U38" s="4" t="s">
@@ -4061,7 +4056,7 @@
         <v>139</v>
       </c>
       <c r="I39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J39" t="s">
         <v>290</v>
@@ -4069,7 +4064,7 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O39" s="16"/>
       <c r="P39"/>
@@ -4113,13 +4108,13 @@
       </c>
       <c r="H40" s="2"/>
       <c r="I40" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J40" t="s">
         <v>290</v>
       </c>
       <c r="N40" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O40" s="16"/>
       <c r="U40" s="4" t="s">
@@ -4158,13 +4153,13 @@
         <v>139</v>
       </c>
       <c r="I41" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J41" t="s">
         <v>290</v>
       </c>
       <c r="N41" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O41" s="16"/>
       <c r="U41" s="4" t="s">
@@ -4203,13 +4198,13 @@
         <v>148</v>
       </c>
       <c r="I42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J42" t="s">
         <v>290</v>
       </c>
       <c r="N42" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O42" s="16"/>
       <c r="U42" s="4" t="s">
@@ -4249,13 +4244,13 @@
       </c>
       <c r="H43" s="2"/>
       <c r="I43" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J43" t="s">
         <v>290</v>
       </c>
       <c r="N43" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O43" s="16"/>
       <c r="U43" s="4" t="s">
@@ -4294,13 +4289,13 @@
         <v>155</v>
       </c>
       <c r="I44" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J44" t="s">
         <v>290</v>
       </c>
       <c r="N44" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O44" s="16"/>
       <c r="U44" s="4" t="s">
@@ -4339,20 +4334,20 @@
         <v>159</v>
       </c>
       <c r="I45" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J45" t="s">
+        <v>345</v>
+      </c>
+      <c r="K45" t="s">
         <v>346</v>
-      </c>
-      <c r="K45" t="s">
-        <v>347</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>300</v>
       </c>
       <c r="M45" s="5"/>
       <c r="N45" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O45" s="16"/>
       <c r="S45" s="2"/>
@@ -4395,20 +4390,20 @@
         <v>162</v>
       </c>
       <c r="I46" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J46" t="s">
+        <v>347</v>
+      </c>
+      <c r="K46" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>349</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>163</v>
       </c>
       <c r="M46" s="5"/>
       <c r="N46" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O46" s="16"/>
       <c r="U46" t="s">
@@ -4448,27 +4443,27 @@
       </c>
       <c r="H47" s="2"/>
       <c r="I47" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J47" t="s">
+        <v>347</v>
+      </c>
+      <c r="K47" t="s">
         <v>348</v>
-      </c>
-      <c r="K47" t="s">
-        <v>349</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>163</v>
       </c>
       <c r="M47" s="5"/>
       <c r="N47" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O47" s="16"/>
       <c r="P47" t="s">
         <v>309</v>
       </c>
       <c r="Q47" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U47" t="s">
         <v>25</v>
@@ -4480,7 +4475,7 @@
         <v>50</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="128.25" x14ac:dyDescent="0.45">
@@ -4506,27 +4501,27 @@
         <v>169</v>
       </c>
       <c r="I48" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J48" t="s">
+        <v>349</v>
+      </c>
+      <c r="K48" t="s">
         <v>350</v>
-      </c>
-      <c r="K48" t="s">
-        <v>351</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>303</v>
       </c>
       <c r="M48" s="5"/>
       <c r="N48" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O48" s="16"/>
       <c r="P48" t="s">
         <v>309</v>
       </c>
       <c r="Q48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U48" t="s">
         <v>25</v>
@@ -4538,7 +4533,7 @@
         <v>37</v>
       </c>
       <c r="X48" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="49" spans="1:25" ht="213.75" x14ac:dyDescent="0.45">
@@ -4564,27 +4559,27 @@
         <v>173</v>
       </c>
       <c r="I49" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J49" t="s">
+        <v>351</v>
+      </c>
+      <c r="K49" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>304</v>
       </c>
       <c r="M49" s="5"/>
       <c r="N49" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O49" s="16"/>
       <c r="P49" t="s">
         <v>309</v>
       </c>
       <c r="Q49" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="S49" s="2"/>
       <c r="U49" t="s">
@@ -4597,7 +4592,7 @@
         <v>50</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>305</v>
@@ -4626,27 +4621,27 @@
         <v>173</v>
       </c>
       <c r="I50" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J50" t="s">
+        <v>353</v>
+      </c>
+      <c r="K50" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>355</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>304</v>
       </c>
       <c r="M50" s="5"/>
       <c r="N50" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O50" s="16"/>
       <c r="P50" t="s">
         <v>309</v>
       </c>
       <c r="Q50" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="S50" s="2"/>
       <c r="U50" t="s">
@@ -4659,7 +4654,7 @@
         <v>50</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y50" s="2" t="s">
         <v>305</v>
@@ -4688,27 +4683,27 @@
         <v>173</v>
       </c>
       <c r="I51" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J51" t="s">
+        <v>355</v>
+      </c>
+      <c r="K51" t="s">
         <v>356</v>
-      </c>
-      <c r="K51" t="s">
-        <v>357</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>180</v>
       </c>
       <c r="M51" s="5"/>
       <c r="N51" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O51" s="16"/>
       <c r="P51" t="s">
         <v>309</v>
       </c>
       <c r="Q51" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U51" t="s">
         <v>25</v>
@@ -4720,7 +4715,7 @@
         <v>50</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="52" spans="1:25" ht="85.5" x14ac:dyDescent="0.45">
@@ -4746,7 +4741,7 @@
         <v>184</v>
       </c>
       <c r="I52" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J52" t="s">
         <v>290</v>
@@ -4754,7 +4749,7 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O52" s="16"/>
       <c r="U52" s="4" t="s">
@@ -4793,27 +4788,27 @@
         <v>173</v>
       </c>
       <c r="I53" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J53" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="K53" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>306</v>
       </c>
       <c r="M53" s="5"/>
       <c r="N53" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O53" s="16"/>
       <c r="P53" t="s">
         <v>309</v>
       </c>
       <c r="Q53" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U53" t="s">
         <v>25</v>
@@ -4825,10 +4820,10 @@
         <v>50</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="54" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -4854,13 +4849,13 @@
         <v>173</v>
       </c>
       <c r="I54" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J54" t="s">
         <v>290</v>
       </c>
       <c r="N54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O54" s="16"/>
       <c r="U54" s="4" t="s">
@@ -4899,7 +4894,7 @@
         <v>173</v>
       </c>
       <c r="I55" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J55" t="s">
         <v>290</v>
@@ -4907,7 +4902,7 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O55" s="16"/>
       <c r="U55" s="4" t="s">
@@ -4946,7 +4941,7 @@
         <v>173</v>
       </c>
       <c r="I56" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J56" t="s">
         <v>290</v>
@@ -4954,7 +4949,7 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O56" s="16"/>
       <c r="U56" s="4" t="s">
@@ -4993,13 +4988,13 @@
         <v>173</v>
       </c>
       <c r="I57" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J57" t="s">
         <v>290</v>
       </c>
       <c r="N57" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O57" s="16"/>
       <c r="U57" s="4" t="s">
@@ -5038,13 +5033,13 @@
         <v>173</v>
       </c>
       <c r="I58" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J58" t="s">
         <v>290</v>
       </c>
       <c r="N58" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O58" s="16"/>
       <c r="U58" s="4" t="s">
@@ -5080,13 +5075,13 @@
         <v>16</v>
       </c>
       <c r="I59" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J59" t="s">
         <v>290</v>
       </c>
       <c r="N59" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O59" s="16"/>
       <c r="U59" s="4" t="s">
@@ -5122,13 +5117,13 @@
         <v>16</v>
       </c>
       <c r="I60" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J60" t="s">
         <v>290</v>
       </c>
       <c r="N60" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O60" s="16"/>
       <c r="U60" s="4" t="s">
@@ -5164,13 +5159,13 @@
         <v>16</v>
       </c>
       <c r="I61" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J61" t="s">
         <v>290</v>
       </c>
       <c r="N61" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O61" s="16"/>
       <c r="U61" s="4" t="s">
@@ -5206,13 +5201,13 @@
         <v>16</v>
       </c>
       <c r="I62" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J62" t="s">
         <v>290</v>
       </c>
       <c r="N62" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O62" s="16"/>
       <c r="U62" s="4" t="s">
@@ -5248,13 +5243,13 @@
         <v>16</v>
       </c>
       <c r="I63" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J63" t="s">
         <v>290</v>
       </c>
       <c r="N63" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O63" s="16"/>
       <c r="S63" s="2"/>
@@ -5292,13 +5287,13 @@
         <v>16</v>
       </c>
       <c r="I64" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J64" t="s">
         <v>290</v>
       </c>
       <c r="N64" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O64" s="16"/>
       <c r="U64" s="4" t="s">
@@ -5335,13 +5330,13 @@
       </c>
       <c r="H65" s="2"/>
       <c r="I65" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J65" t="s">
         <v>290</v>
       </c>
       <c r="N65" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O65" s="16"/>
       <c r="U65" s="4" t="s">
@@ -5380,27 +5375,27 @@
         <v>214</v>
       </c>
       <c r="I66" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J66" t="s">
+        <v>359</v>
+      </c>
+      <c r="K66" t="s">
         <v>360</v>
-      </c>
-      <c r="K66" t="s">
-        <v>361</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>306</v>
       </c>
       <c r="M66" s="5"/>
       <c r="N66" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O66" s="16"/>
       <c r="P66" t="s">
         <v>309</v>
       </c>
       <c r="Q66" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="S66" s="2"/>
       <c r="U66" t="s">
@@ -5413,7 +5408,7 @@
         <v>37</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Y66" s="2"/>
     </row>
@@ -5441,13 +5436,13 @@
       </c>
       <c r="H67" s="2"/>
       <c r="I67" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J67" t="s">
         <v>290</v>
       </c>
       <c r="N67" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O67" s="16"/>
       <c r="U67" s="4" t="s">
@@ -5486,13 +5481,13 @@
         <v>220</v>
       </c>
       <c r="I68" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J68" t="s">
         <v>290</v>
       </c>
       <c r="N68" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O68" s="16"/>
       <c r="U68" s="4" t="s">
@@ -5531,27 +5526,27 @@
         <v>223</v>
       </c>
       <c r="I69" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J69" t="s">
+        <v>361</v>
+      </c>
+      <c r="K69" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>307</v>
       </c>
       <c r="M69" s="5"/>
       <c r="N69" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O69" s="16"/>
       <c r="P69" t="s">
         <v>309</v>
       </c>
       <c r="Q69" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U69" t="s">
         <v>25</v>
@@ -5563,7 +5558,7 @@
         <v>50</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="70" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
@@ -5589,13 +5584,13 @@
         <v>226</v>
       </c>
       <c r="I70" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J70" t="s">
         <v>290</v>
       </c>
       <c r="N70" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O70" s="16"/>
       <c r="U70" s="4" t="s">
@@ -5634,13 +5629,13 @@
         <v>226</v>
       </c>
       <c r="I71" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J71" t="s">
         <v>290</v>
       </c>
       <c r="N71" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O71" s="16"/>
       <c r="U71" s="4" t="s">
@@ -5677,13 +5672,13 @@
       </c>
       <c r="H72" s="2"/>
       <c r="I72" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J72" t="s">
         <v>290</v>
       </c>
       <c r="N72" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O72" s="16"/>
       <c r="U72" s="4" t="s">
@@ -5722,13 +5717,13 @@
         <v>234</v>
       </c>
       <c r="I73" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J73" t="s">
         <v>290</v>
       </c>
       <c r="N73" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O73" s="16"/>
       <c r="U73" s="4" t="s">
@@ -5767,13 +5762,13 @@
         <v>238</v>
       </c>
       <c r="I74" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J74" t="s">
         <v>290</v>
       </c>
       <c r="N74" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O74" s="16"/>
       <c r="U74" s="4" t="s">
@@ -5812,13 +5807,13 @@
         <v>242</v>
       </c>
       <c r="I75" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J75" t="s">
         <v>290</v>
       </c>
       <c r="N75" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O75" s="16"/>
       <c r="U75" s="4" t="s">
@@ -5858,13 +5853,13 @@
       </c>
       <c r="H76" s="2"/>
       <c r="I76" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J76" t="s">
         <v>290</v>
       </c>
       <c r="N76" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O76" s="16"/>
       <c r="S76" s="2"/>
@@ -5905,13 +5900,13 @@
         <v>249</v>
       </c>
       <c r="I77" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J77" t="s">
         <v>290</v>
       </c>
       <c r="N77" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O77" s="16"/>
       <c r="U77" s="4" t="s">
@@ -5950,13 +5945,13 @@
         <v>253</v>
       </c>
       <c r="I78" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J78" t="s">
         <v>290</v>
       </c>
       <c r="N78" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O78" s="16"/>
       <c r="U78" s="4" t="s">
@@ -5995,13 +5990,13 @@
         <v>256</v>
       </c>
       <c r="I79" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J79" t="s">
         <v>290</v>
       </c>
       <c r="N79" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O79" s="16"/>
       <c r="U79" s="4" t="s">
@@ -6040,27 +6035,27 @@
         <v>173</v>
       </c>
       <c r="I80" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J80" t="s">
+        <v>392</v>
+      </c>
+      <c r="K80" t="s">
+        <v>397</v>
+      </c>
+      <c r="L80" s="5" t="s">
         <v>393</v>
-      </c>
-      <c r="K80" t="s">
-        <v>398</v>
-      </c>
-      <c r="L80" s="5" t="s">
-        <v>394</v>
       </c>
       <c r="M80" s="5"/>
       <c r="N80" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O80" s="16"/>
       <c r="P80" t="s">
         <v>309</v>
       </c>
       <c r="Q80" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="S80" s="2"/>
       <c r="U80" t="s">
@@ -6073,10 +6068,10 @@
         <v>50</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Y80" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="81" spans="1:25" ht="99.75" x14ac:dyDescent="0.45">
@@ -6102,27 +6097,27 @@
         <v>173</v>
       </c>
       <c r="I81" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J81" t="s">
+        <v>363</v>
+      </c>
+      <c r="K81" t="s">
         <v>364</v>
-      </c>
-      <c r="K81" t="s">
-        <v>365</v>
       </c>
       <c r="L81" s="5" t="s">
         <v>308</v>
       </c>
       <c r="M81" s="5"/>
       <c r="N81" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O81" s="16"/>
       <c r="P81" t="s">
         <v>309</v>
       </c>
       <c r="Q81" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U81" t="s">
         <v>25</v>
@@ -6134,7 +6129,7 @@
         <v>50</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="82" spans="1:25" ht="71.25" x14ac:dyDescent="0.45">
@@ -6160,27 +6155,27 @@
         <v>173</v>
       </c>
       <c r="I82" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J82" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="K82" s="6" t="s">
         <v>381</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>382</v>
       </c>
       <c r="L82" s="5"/>
       <c r="M82" s="5" t="s">
         <v>13</v>
       </c>
       <c r="N82" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O82" s="16"/>
       <c r="P82" t="s">
         <v>309</v>
       </c>
       <c r="Q82" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="S82" s="2"/>
       <c r="U82" t="s">
@@ -6196,7 +6191,7 @@
         <v>14</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="83" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
@@ -6219,13 +6214,13 @@
         <v>49</v>
       </c>
       <c r="I83" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>290</v>
       </c>
       <c r="N83" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O83" s="16"/>
       <c r="U83" s="4" t="s">
@@ -6264,7 +6259,7 @@
         <v>272</v>
       </c>
       <c r="I84" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>290</v>
@@ -6272,7 +6267,7 @@
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
       <c r="N84" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O84" s="16"/>
       <c r="U84" s="4" t="s">

--- a/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-NHATS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17bc974f5891b333/Documents/ProPASS/Harmo/NHATS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="8_{B04BC2F6-0886-423B-9CF8-2AF8452D03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3921F31C-8E7E-479F-8418-8CCBAC8E8062}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{B04BC2F6-0886-423B-9CF8-2AF8452D03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49363FE2-4286-4BF7-BA46-81E5E7569B2A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F744FAC3-0BAB-4C7A-92B3-0824573F48DB}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="401">
   <si>
     <t>index</t>
   </si>
@@ -2872,7 +2872,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:25" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>15</v>
       </c>
@@ -3357,6 +3357,18 @@
       <c r="O23" s="16"/>
       <c r="P23" t="s">
         <v>309</v>
+      </c>
+      <c r="U23" t="s">
+        <v>14</v>
+      </c>
+      <c r="V23" t="s">
+        <v>15</v>
+      </c>
+      <c r="W23" t="s">
+        <v>14</v>
+      </c>
+      <c r="X23" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
